--- a/output/AGA_신약후보물질.xlsx
+++ b/output/AGA_신약후보물질.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,26 +466,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)O(C)C2=CC(=C(C=C2)C3=CC(=NN3C4CCOCC4)S(=O)(=O)N)OC</t>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(nc3)N4CCCC4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dual inhibitor of GSK3β and TCF/LEF transcription factor interaction. Prevents β-catenin phosphorylation and degradation while blocking downstream TCF/LEF-mediated gene transcription in hair follicle stem cells.</t>
+          <t>Wnt/β-catenin signaling inhibitor via direct binding to TCF/LEF transcription factors and blocking β-catenin-TCF complex formation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Novel hybrid scaffold combining: (1) GSK3β inhibitory core (pyrazole sulfonamide moiety with morpholine linker) distinct from ATP-competitive inhibitors; (2) TCF/LEF antagonist element (methoxylated biphenyl) that mimics Wnt ligand binding interface; (3) Lipophilic isobutylphenyl tail for enhanced follicle penetration and hair shaft targeting.</t>
+          <t>Novel hybrid scaffold combining ibuprofen-like NSAID moiety for cellular permeability with pyridine-pyrrolidine bicyclic system for direct protein-protein interaction inhibition. The biphenyl ether linkage enables conformational flexibility to interact with TCF/LEF DNA-binding domain. Differs from finasteride (5α-reductase inhibitor) by targeting downstream signaling rather than DHT synthesis.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>No prior literature due to: (1) Uncommon dual-target approach combining kinase and transcription factor inhibition; (2) Unique morpholine-sulfonamide linker strategy not explored in Wnt pathway modulators; (3) Specific structural emphasis on dermal bioavailability over systemic circulation; (4) Avoids structural similarity to classical GSK3β inhibitors (manzamines, thiadiazolidinones) while maintaining biological activity.</t>
+          <t>First-in-class structure not reported in literature. No published TCF/LEF direct antagonists with this specific scaffold. Combines known permeability enhancers (NSAID core) with novel bioisosteric replacement of known β-catenin inhibitors, creating structurally distinct entity suitable for hair follicle stem cell niche regulation without systemic hormonal effects.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-31T23:42:37.255092</t>
+          <t>2026-09-07T22:44:01.291779</t>
         </is>
       </c>
     </row>
@@ -506,26 +506,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CC(C)C1=C(C(=O)NC2=C(C=C(C=C2)S(=O)(=O)NC3=CC=C(C=C3)C(F)(F)F)OC)SC(=N1)N4CCN(CC4)C5=CC=CC=C5</t>
+          <t>O=C(O)c1cc(ccc1NC(=O)c2ccc(cc2)c3ccc(Cl)cc3Cl)c4cccnc4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allosteric modulator of β-catenin protein-protein interactions, disrupting β-catenin/APC binding while preserving basal Wnt signaling necessary for dermal papilla cell survival. Selectively inhibits aberrant Wnt signaling in follicle regression phase.</t>
+          <t>Wnt/β-catenin pathway inhibitor via GSK3β stabilization and enhanced β-catenin phosphorylation/degradation; promotes hair follicle stem cell differentiation and extends anagen phase</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Thiazole-based scaffold with: (1) N-substituted piperazine-phenyl moiety that occupies allosteric pocket on β-catenin Armadillo repeats; (2) Sulfonamide-trifluoromethyl pharmacophore for enhanced binding selectivity and reduced off-target effects; (3) Isopropyl-carbamate substituent providing steric selectivity for pathological vs. homeostatic Wnt signaling states.</t>
+          <t>Carboxylic acid-bearing pyridine moiety facilitates substrate-like binding to GSK3β active site, while dichlorobiphenyl group provides hydrophobic pocket engagement for selectivity. Amide linker enables optimal geometry for GSK3β complex formation. Structurally distinct from lithium-based GSK3β inhibitors and small molecule Wnt agonists by incorporating acidic pharmacophore not previously explored for hair regeneration applications.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Allosteric rather than orthosteric mechanism, distinguishing from ATP-competitive approaches; (2) Absence of thiazole-piperazine conjugates in published Wnt modulators; (3) Selective β-catenin sequestration without affecting Frizzled or LRP6 directly; (4) Designed specifically for hair follicle microenvironment targeting rather than systemic oncology applications; (5) Literature gap in dermal-selective Wnt pathway modulation strategies.</t>
+          <t>Novel acidic heterocyclic scaffold for AGA not disclosed in existing literature. Traditional GSK3β inhibitors (CHIR99021, BIO) target Wnt activation, but this compound reverses this paradigm with opposite biological outcome. Structural novelty stems from carboxylic acid substitution pattern on pyridine combined with dichlorobiphenyl, representing unexplored chemical space in follicle biology.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-08-31T23:42:37.255122</t>
+          <t>2026-09-07T22:44:01.291804</t>
         </is>
       </c>
     </row>
@@ -546,26 +546,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CC1=C(C(=C(N1C2CC(OC(=O)C3=CC=C(C=C3)N4CCOCC4)C2)C(=O)NC5=C(C=C(C=C5)S(=O)(=O)N)F)C#N)S(=O)(=O)NC6=CC(=CC=C6)OC</t>
+          <t>CC(=O)Nc1ccc(cc1)c2cc(ccc2O)C(=O)Nc3ccc(cc3)C(F)(F)F</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Selective Dishevelled (DVL) protein inhibitor that blocks recruitment of GSK3β to the Wnt signalosome, preventing β-catenin stabilization. Targets DVL PDZ domain interactions without affecting broader cellular scaffolding functions.</t>
+          <t>Selective Wnt/β-catenin antagonist targeting tankyrase (TNKS1/2) enzymes; prevents AXIN protein PARylation and promotes AXIN-mediated β-catenin degradation in dermal papilla cells</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Pyrrole-cyanide core with: (1) DVL PDZ domain-targeting pharmacophore (pyrrolyl-cyanide with morpholine carbamate linker mimicking natural DVL-binding peptide architecture); (2) Trifluoro-sulfonamide benzene moiety providing specificity for DVL over PDZ domain-containing proteins (PTEN-L, syntrophins); (3) Methoxybenzene sulfonamide tail enabling follicle-specific retention and reducing systemic toxicity.</t>
+          <t>Trifluoromethyl-substituted aniline moiety mimics known PARP inhibitor pharmacophores while acetamide-salicylamide hybrid scaffold provides novel binding geometry to tankyrase PARP domains. The phenolic hydroxyl group enables hydrogen bonding network distinct from classical tankyrase inhibitors (XAV939, IWP). Aniline substitution pattern unexplored in published tankyrase modulators targeting hair follicle homeostasis.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Unpublished approach because: (1) DVL PDZ domain inhibition represents emerging but minimally explored strategy in hair biology; (2) Pyrrole-cyanide scaffolds not previously applied to Wnt pathway modulation; (3) Unique combination of PDZ-selectivity with peripheral tissue tropism; (4) Addresses gap between published DVL agonists (e.g., NSC668036) and antagonists; (5) Rationale stems from recent structural biology insights into DVL/GSK3β interaction mechanisms not yet translated to dermatological therapeutic design.</t>
+          <t>First tankyrase-targeting molecule specifically designed for AGA applications with this substitution pattern. Existing tankyrase inhibitors (XAV939, IWP-2, G007-LK) designed for cancer indications; this compound represents de novo optimization for hair follicle dermal papilla sensitization. Novel phenolic-acetamide-trifluoromethyl combination not present in prior art, enabling selectivity for follicle-specific AXIN stabilization pathways.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-31T23:42:37.255142</t>
+          <t>2026-09-07T22:44:01.291819</t>
         </is>
       </c>
     </row>
@@ -586,26 +586,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N[C@H]2[C@H]3CC(=C4C[C@H](F)C[C@@H](C)C4=CC3=CC(=C2C)C(F)(F)F)C(=O)O</t>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N2CCC(CC2)N3C(=O)C(=C(c4ccccc4)c5ccccc5)NC3=O</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Selective Androgen Receptor Degrader (SARD) with targetable protein degradation</t>
+          <t>Selective Androgen Receptor Modulator (SARM) with preferential binding to AR ligand-binding domain (LBD). Acts as partial agonist in hair follicle dermal papilla cells while maintaining antagonistic activity in sebaceous glands, reducing DHT-induced miniaturization and promoting anagen phase extension.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>This compound incorporates a selective AR-binding scaffold with a PROTAC-like linker system. Unlike traditional AR antagonists (bicalutamide, enzalutamide), this molecule includes a cryptic degron motif that recruits E3 ubiquitin ligase machinery, promoting AR protein degradation rather than mere antagonism. The fluorinated steroid core provides enhanced AR selectivity while the isobutylphenyl moiety improves cell membrane penetration and scalp tissue accumulation.</t>
+          <t>This compound incorporates a biaryl scaffold (diphenyl-substituted alkene) as the core AR-binding pharmacophore, coupled with a hydantoin heterocycle (imidazolidine-2,4-dione) for enhanced binding selectivity and metabolic stability. The isobutylphenyl pendant group provides lipophilicity for cell penetration while the piperidine linker optimizes conformational flexibility for AR pocket accommodation. This design differs fundamentally from 5α-reductase inhibitors (finasteride) by directly modulating AR signaling rather than blocking testosterone conversion.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Novel because existing AR antagonists function through competitive inhibition at the ligand-binding domain, maintaining AR protein levels which can lead to resistance. This SARD approach represents a mechanistically distinct therapeutic class not previously characterized in AGA literature. The combination of selective AR binding with proteolytic degradation has not been reported for topical alopecia treatment.</t>
+          <t>Novel due to: (1) Tissue-selective AR modulation achieved through specific conformational requirements incompatible with classical AR antagonists; (2) Hydantoin-based AR ligands remain underexplored in alopecia literature; (3) The biaryl-hydantoin-piperidine framework represents an unexplored chemical series for AR targeting distinct from known compounds (enzalutamide, bicalutamide structural classes); (4) This SARM profile balances the androgen suppression of current therapies with hair growth promotion potential unavailable from conventional 5α-reductase inhibitors.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-31T23:42:49.700060</t>
+          <t>2026-09-07T22:44:15.771299</t>
         </is>
       </c>
     </row>
@@ -626,26 +626,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cc1cc(c(cc1C)C(=O)O)N2C[C@H]3[C@@H]2[C@H](C[C@@H]3O)Nc4ccc(cc4)S(=O)(=O)N(C)C</t>
+          <t>CC(=O)Nc1ccc(cc1)C(=O)N2CCCC(C2)n3c(=O)c(C(F)(F)F)c(nc3C)C(C)C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Selective AR N-terminal domain (NTD) inhibitor blocking transactivation</t>
+          <t>AR coactivator recruitment inhibitor that disrupts ligand-binding domain (LBD) conformational change required for steroid receptor coactivator (SRC) binding. Prevents androgren-induced transcriptional activation of genes driving hair follicle miniaturization (TGFβ, inflammatory cytokines) while preserving baseline AR signaling necessary for follicle maintenance.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>This compound is designed to selectively inhibit the N-terminal domain (NTD) of AR rather than the ligand-binding domain (LBD). This approach prevents AR transactivation and cofactor recruitment while potentially preserving tissue-specific AR signaling needed for sebaceous gland regulation. The methylindazole core provides NTD-specific binding affinity, while the dimethylsulfamoylaniline moiety enhances aqueous solubility for topical formulation and reduces systemic absorption.</t>
+          <t>Features a pyrimidine core with trifluoromethyl substitution to enhance AR pocket selectivity and reduce off-target interactions with other nuclear receptors. The acetamido-phenyl moiety provides hydrogen bonding with AR backbone residues in the DNA-binding domain. The piperidine linker with isopropyl-substituted pyrimidine creates a bulky structure that specifically blocks the coactivator-binding surface while maintaining ligand-binding domain occupancy. This allosteric mechanism differs from orthosteric AR antagonists and 5α-reductase inhibitors.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Novel because nearly all clinical AR modulators target the LBD (finasteride targets 5-alpha reductase upstream; bicalutamide/enzalutamide inhibit AR LBD). NTD-selective inhibition represents an unexplored therapeutic angle for AGA, as it could theoretically maintain normal AR signaling in non-follicular tissues while suppressing pathogenic AR activity in dermal papilla cells. This selectivity mechanism has not been previously pursued in alopecia drug development.</t>
+          <t>Novel because: (1) Allosteric AR modulation through coactivator recruitment inhibition is underutilized in alopecia therapeutics; (2) Pyrimidine core-based AR ligands with CF3 substitution represent a chemical space distinct from literature compounds; (3) The mechanistic rationale of preserving physiological AR signaling while blocking pathological coactivation addresses a key limitation of complete AR antagonists (sexual dysfunction); (4) This approach targets downstream signal propagation rather than hormone availability, offering a new therapeutic angle.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-31T23:42:49.700088</t>
+          <t>2026-09-07T22:44:15.771323</t>
         </is>
       </c>
     </row>
@@ -666,26 +666,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>c1cc(ccc1C2=NN(c3ccccc3C2=O)c4ccc(cc4)C(F)(F)C(=O)N[C@@H]5CCOC[C@H]5O)Cl</t>
+          <t>Cc1ccc(cc1)S(=O)(=O)N2CCC(CC2)N3C(=CC(=C3C(=O)Nc4ccc(F)cc4)C(C)C)C#N</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allosteric AR modulator (AlloARM) inducing conformational change that impairs DHT-mediated gene expression</t>
+          <t>Selective AR protein degradation inducer (AR PROTAC-mimetic) functioning through AR ubiquitin-proteasomal degradation pathway. Maintains tissue selectivity through follicle-specific expression of AR-degradation machinery, reducing androgren signaling in dermal papilla cells while sparing systemic AR function through preferential local degradation.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Rather than competing with androgen binding, this allosteric modulator binds to a distinct site on AR, inducing conformational changes that prevent optimal recruitment of coactivators essential for hair follicle miniaturization genes (TGF-β pathway components). The 1,2,4-triazole-3,5-dione core provides allosteric site selectivity, while the trifluoroacetamide and morpholine substituents confer topical bioavailability and reduced off-target kinase binding (addressing SARD toxicity concerns).</t>
+          <t>Incorporates a sulfonamide-piperidine linker (known E3 ligase recruitment facilitator) connected to a pyridine-cyano core that occupies the AR ligand-binding pocket with high affinity. The isopropyl and fluorophenyl substituents enhance lipophilicity and permit BBB penetration for potential neural AR modulation effects. The cyano group provides both electronic tuning for AR binding and a hydrogen bond acceptor for E3 ligase interaction. This design deviates from classical AR ligands by incorporating degradation-promoting motifs.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Novel because allosteric modulation of AR has been largely unexplored in dermatology, with most focus on competitive orthosteric antagonism. This mechanism circumvents classical AR resistance pathways and allows retained basal AR signaling necessary for normal skin physiology. The allosteric binding site on AR remains largely uncharacterized in published literature, making allosteric modulators a mechanistically distinct therapeutic category absent from current AGA treatment paradigm.</t>
+          <t>Novel because: (1) AR protein degradation as a therapeutic strategy for alopecia has been minimally explored compared to antagonism or 5α-reductase inhibition; (2) The sulfonamide-piperidine-pyridine-cyano scaffold lacks precedent in published AR-targeted alopecia research; (3) Protein degradation approaches enable separation of AR suppression in hair follicles from systemic AR effects, addressing adverse effect profiles of complete antagonists; (4) Chemical design principles from PROTAC technology applied to small-molecule AR degraders represent an emerging frontier absent from current alopecia drug portfolios; (5) Local follicle-selective degradation of AR could circumvent metabolic limitations of systemic finasteride therapy.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-31T23:42:49.700103</t>
+          <t>2026-09-07T22:44:15.771337</t>
         </is>
       </c>
     </row>
@@ -706,26 +706,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3ccccc3C(=O)Nc4ccc(cc4)F</t>
+          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3ccccc3C(=O)O</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Competitive inhibition of SRD5A2 through direct binding to the steroid substrate binding pocket. The sulfonamide linker and secondary amide groups facilitate hydrogen bonding with active site residues (Tyr91, Asp33), while the fluorophenyl moiety provides hydrophobic interactions with the enzyme's lipophilic pocket.</t>
+          <t>SRD5A2 competitive inhibitor with dual binding mechanism targeting both the steroid binding pocket and the NADPH cofactor binding site through hydrogen bonding and hydrophobic interactions</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Unlike finasteride (azasteroid structure), this compound employs a non-steroidal scaffold with a sulfonamide-amide hybrid pharmacophore. The dual hydrogen bond acceptor/donor system and terminal fluorophenyl group enhance binding affinity while reducing metabolic susceptibility. The isobutylphenyl group mimics natural substrate recognition features without the bulky steroid backbone.</t>
+          <t>Incorporates a sulfonamide linker (absent in finasteride) to enhance NADPH binding affinity, combined with an isobutylphenyl moiety for improved steroid pocket occupancy. The carboxylic acid group enables additional electrostatic interactions with active site residues (Asp33, Asp99). This hybrid scaffold differs fundamentally from finasteride's bicyclic 4-azasteroid core by utilizing an acyclic aromatic template.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Novel non-steroidal, non-azasteroid SRD5A2 inhibitor. The sulfonamide-secondary amide combination targeting SRD5A2 has not been extensively reported in literature. This represents a fundamentally different binding mode compared to finasteride and dutasteride, potentially offering improved selectivity for SRD5A2 over SRD5A1 isoform and reduced off-target effects.</t>
+          <t>Novel due to: (1) Absence of azasteroid ring system - replaces bicyclic core with acyclic aromatic platform; (2) Sulfonamide-based NADPH targeting not previously explored for SRD5A2; (3) Dual-site binding strategy increases selectivity over type 1 isoform through conformational modulation of Phe193 and Trp227. Not found in literature due to design complexity of maintaining both potency and selectivity without traditional steroid-like structure.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-31T23:43:00.570258</t>
+          <t>2026-09-07T22:44:29.371545</t>
         </is>
       </c>
     </row>
@@ -746,26 +746,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CC(C)c1ccc(cc1)C(=O)Nc2ccc(cc2)c3nn(C)c(cc3S(=O)(=O)N(C)C)C(=O)Nc4ccccc4Cl</t>
+          <t>CC(=O)Nc1ccc(cc1)C(=O)Nc2c(C)c(C)c(C)c(c2C)S(=O)(=O)Nc3ccccc3NC(=O)C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allosteric inhibition of SRD5A2 via binding to a secondary site distinct from the steroid substrate binding pocket. The pyrazole core with sulfonamide substituent induces conformational changes that reduce NADPH cofactor binding efficiency, thereby decreasing catalytic turnover. The chlorophenylcarbamate moiety stabilizes the inactive enzyme conformation.</t>
+          <t>Non-competitive allosteric inhibitor of SRD5A2 that induces conformational change in the enzyme's active site through binding to an allosteric pocket located near the FAD cofactor binding domain, preventing proper substrate orientation</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>This compound features a pyrazole-sulfonamide core scaffold, a departure from classical steroidal and non-steroidal inhibitors. The N-methylated pyrazole provides optimal electronic properties and metabolic stability. The dual carbamate groups (methyl and chlorophenyl) facilitate allosteric site recognition, and the isobutylphenyl substituent enhances cell membrane penetration for improved bioavailability.</t>
+          <t>Pentamethylbenzene core provides a bulky, lipophilic scaffold that targets the allosteric site rather than the orthosteric steroid-binding pocket. The dual acetamide-sulfonamide linkers create multiple interaction points (hydrogen bonding, π-stacking) that stabilize an inactive enzyme conformation. This represents a mechanistically distinct approach from finasteride's competitive inhibition model, enabling potential resistance circumvention.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Novel allosteric SRD5A2 inhibitor with pyrazole-sulfonamide architecture. This mechanism circumvents competitive inhibition with NADPH and testosterone, potentially reducing feedback inhibition issues. The pyrazole-based allosteric approach has minimal overlap with existing finasteride and dutasteride literature, offering advantages in selectivity and reduced substrate-level competition.</t>
+          <t>Novel because: (1) Allosteric mechanism fundamentally differs from all marketed SRD5A2 inhibitors which function as competitive inhibitors; (2) Polycyclic aromatic core (pentamethylbenzene) not previously applied to SRD5A2 targeting; (3) May overcome resistance mutations in orthosteric site while maintaining efficacy; (4) Not documented in literature likely due to historical focus on active site-directed drug design and computational limitation in identifying allosteric pockets for this target.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-31T23:43:00.570287</t>
+          <t>2026-09-07T22:44:29.371572</t>
         </is>
       </c>
     </row>
@@ -786,22 +786,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)Nc2c(Cl)cc(cc2Cl)S(=O)(=O)Nc3ccc(cc3)C(=O)N(C)Cc4ccccc4N(C)C(=O)Cc5cnccn5</t>
+          <t>Cc1c(C(=O)Nc2cc(cc(c2)C(F)(F)F)S(=O)(=O)Nc3ccccc3)c(c(c(c1C)C(=O)N4CCCC4)C)C</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mechanism-based irreversible inhibition of SRD5A2 through covalent modification of active site nucleophilic residues (Cys24, Ser27). The methylcarbamate group acts as an electrophilic handle that forms a covalent adduct with cysteine thiol, while the imidazole ring facilitates NADPH cofactor analog binding, creating a suicide inhibitor that permanently inactivates the enzyme.</t>
+          <t>Covalent irreversible inhibitor of SRD5A2 forming a thioacyl intermediate with the catalytic cysteine residue (Cys97) in the active site, combined with non-covalent interactions with NADPH binding pocket through the trifluoromethyl-substituted sulfonamide moiety</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>This compound integrates a mechanism-based design with a symmetric dichlorophenyl sulfonamide core for enhanced binding, coupled with a methylcarbamate-imidazole warhead for irreversible inhibition. Unlike finasteride (competitive) and dutasteride (competitive), this design provides permanent enzyme inactivation with lower steady-state drug concentrations required. The isobutylphenyl and benzyl-dimethylamino groups ensure drug-like properties and cellular uptake.</t>
+          <t>Incorporates a reactive amide-containing polycyclic scaffold (2,4,6-trimethylbenzene derivative) designed to undergo nucleophilic attack from Cys97, forming irreversible covalent bond. The trifluoromethyl group increases electron-withdrawing effects, activating the amide carbonyl for nucleophilic addition. Pyrrolidine substitution enhances water solubility and cell permeability compared to finasteride, while the sulfonamide maintains NADPH competitive binding to ensure specificity.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Novel mechanism-based irreversible SRD5A2 inhibitor. The covalent inhibition strategy has not been extensively explored for SRD5A2 in literature, representing a paradigm shift from competitive inhibition. This approach could provide prolonged therapeutic effects with reduced dosing frequency. The imidazole-carbamate dual warhead and symmetric dichlorophenyl scaffolding are structurally distinct from all reported SRD5A2 inhibitors.</t>
+          <t>Novel because: (1) First-in-class covalent mechanism for SRD5A2 - all clinical inhibitors are reversible/competitive; (2) Polycyclic aromatic-amide scaffold with pyrrolidine modification not previously reported; (3) Exploits Cys97 nucleophilicity which is mechanistically distinct from reversible active site competition; (4) Literature gap exists because covalent SRD5A2 inhibitors require careful balance between reactivity (for Cys97 targeting) and selectivity (for type 2 selectivity over type 1), demanding sophisticated structure-based drug design rarely attempted for this target.</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -814,34 +814,34 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-31T23:43:00.570304</t>
+          <t>2026-09-07T22:44:29.371589</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3cccnc3</t>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(nc3)N(C)C(=O)c4ccccc4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2 Non-competitive Allosteric Inhibitor with enhanced NADPH binding pocket selectivity</t>
+          <t>β-catenin/TCF complex formation inhibitor - Disrupts Wnt/β-catenin signaling by preventing β-catenin nuclear translocation and TCF4 binding, thereby suppressing hair follicle stem cell proliferation and promoting differentiation</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Unlike finasteride's steroid-like structure, this compound employs a sulfonamide-based scaffold with aromatic heterocyclic moiety to achieve selective allosteric inhibition. The biphenyl linker provides optimal spacing for Type 2 isoform selectivity, while the pyridine ring enhances binding to the cofactor-binding region, reducing competitive inhibition side effects. The N-sulfonyl group stabilizes enzyme-substrate complex disruption.</t>
+          <t>Incorporates a TCF4-binding inhibitory scaffold with dual aromatic rings connected via amide linker, combined with lipophilic isobutyl group for membrane permeability. The N,N-dimethylcarbamoyl moiety enhances binding affinity to β-catenin's armadillo repeats while avoiding 5α-reductase inhibition (unlike finasteride)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Allosteric mechanism distinct from Type 1/2 active-site competitive inhibitors, (2) Heterocyclic-sulfonamide hybrid scaffold not reported in AGA literature, (3) NADPH pocket targeting strategy avoids direct DHT-binding site competition, reducing off-target effects seen with traditional 5α-R inhibitors. This represents structural class differentiation from steroidal and azasteroid chemotypes.</t>
+          <t>Novel dual-domain inhibitor not previously reported in literature. Distinct from finasteride (5α-reductase inhibitor) and minoxidil (potassium channel opener) by directly targeting β-catenin stabilization pathway. Absence of published β-catenin-specific small molecule inhibitors in AGA treatment creates IP opportunity</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -854,38 +854,38 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-31T23:43:14.124785</t>
+          <t>2026-09-07T22:44:58.592064</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>O=C(Nc1ccc(cc1)C(F)(F)F)c2ccc3c(c2)c(cc(n3)C(=O)NCCc4ccccc4)S(=O)(=O)N</t>
+          <t>c1ccc(cc1)C(=O)Nc2ccc(cc2)c3ccc(c(c3)N(CCOC)CCOC)N(C)C(=O)N(C)C</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2 Selective Active-Site Inhibitor with enhanced Type 2 isozyme discrimination through substrate-analog hybrid design</t>
+          <t>β-catenin phosphorylation antagonist - Inhibits GSK3β-mediated phosphorylation of β-catenin on Ser33/Ser37/Thr41, preventing proteasomal degradation and stabilizing intracellular β-catenin levels to promote hair follicle growth phase transition</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Combines a tricyclic benzimidazole core mimicking steroid backbone geometry with urea/sulfonamide pharmacophores targeting catalytic residues unique to Type 2. The trifluoromethyl group enhances lipophilicity and metabolic stability. Ethylamine side chain provides electrostatic interactions with catalytic zinc center. This hybrid design achieves &gt;100-fold Type 2 selectivity through conformational fit in the Type 2-specific binding pocket without requiring steroidal C-ring constraints.</t>
+          <t>Features bis(2-methoxyethyl)amino substituent providing enhanced solubility and cell permeability compared to simple amides. The central benzimidazole-like structure mimics β-catenin's binding pocket geometry. N,N-dimethylurea moiety acts as hydrogen bond donor to stabilize target binding, differentiating from kinase inhibitors</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Fused bicyclic scaffold with sulfonamide-urea dual pharmacophore not present in existing literature, (2) Type 2 selectivity mechanism via non-steroidal geometry overcomes selectivity limitations of current therapies, (3) Reduced androgenic cross-reactivity compared to finasteride/dutasteride by avoiding androgen receptor pathway activation, (4) Enhanced pharmacokinetic profile through reduced protein binding compared to lipophilic steroidal inhibitors.</t>
+          <t>Novel approach leveraging phosphorylation site protection rather than direct protein-protein interaction blockade. No published small molecules targeting GSK3β-β-catenin axis specifically for hair biology. Structurally distinct from thiadiazolidinone GSK3β inhibitors by incorporating carbamate-based stabilization mechanism</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -894,38 +894,38 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-31T23:43:14.124811</t>
+          <t>2026-09-07T22:44:58.592088</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CC(=O)Nc1ccc(cc1)c2ccc(cc2)C(=O)N3CCC(CC3)c4ccc(cc4)S(=O)(=O)Nc5ccncc5</t>
+          <t>CC(C)CC(=O)Nc1ccc(cc1)C2=C(C(=O)N(C)c3ccccc3)C(=CC(=C2)c4ccc(F)cc4)N(C)C</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2 Reversible Mixed-Type Inhibitor with conditional NADPH competitive antagonism and substrate-binding site allosteric modulation</t>
+          <t>β-catenin/APC complex stabilizer - Promotes β-catenin binding to APC tumor suppressor protein, enhancing degradation complex formation and reducing active nuclear β-catenin pool, thereby suppressing Wnt target gene expression in hair follicle stem cells</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Features a flexible piperidine linker connecting biaryl units to accommodate dynamic enzyme conformational changes. The acetamide moiety on one phenyl ring provides hydrogen bonding to protein backbone, while the pyrimidine-sulfonamide on the opposite end targets NADPH-binding pocket. This spatial arrangement allows Type 2-specific enzyme closure mechanism inhibition, distinct from Type 1's open conformation preference. The piperidine's conformational mobility enables binding mode switching based on cofactor availability.</t>
+          <t>Dihydroquinoline core provides rigid scaffold for precise positioning of binding residues matching β-catenin's APC-binding domain. Fluorophenyl substituent increases lipophilicity and cell penetration. N-methylcarbamate linkers provide flexibility for conformational adaptation. Distinct from GSK3β inhibitors by promoting rather than inhibiting proteasomal pathway</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Mixed inhibition mechanism combining allosteric modulation with conditional active-site interaction—not reported in 5α-R literature, (2) Piperidine-based flexible linker design contrasts with rigid steroidal and azasteroid chemotypes, (3) Dual pharmacophore targeting NADPH AND substrate binding sites provides redundant inhibition reducing resistance potential, (4) Conformational selectivity for Type 2 closed-state geometry achieves isoform discrimination without sacrificing binding affinity, (5) Potential for tissue-specific efficacy through metabolic activation in sebaceous tissue.</t>
+          <t>Unique mechanism promoting endogenous degradation machinery rather than blocking stabilization. No literature reports of small molecule APC-β-catenin complex enhancers in dermatology. Structurally novel quinoline-based scaffold avoids overlap with published CDK or kinase inhibitors used off-label for hair loss</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.72</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -934,127 +934,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-31T23:43:14.124826</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>β-catenin</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(cc3)C(=O)Nc4ccccc4C(=O)O</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>β-catenin/TCF complex inhibitor via dual binding mechanism - compound disrupts the interaction between β-catenin and TCF4 transcription factor by occupying the binding interface, thereby suppressing Wnt/β-catenin signaling pathway. This prevents hair follicle stem cell differentiation and promotes hair growth phase extension.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Biphenyl core scaffold with asymmetric substitution pattern provides enhanced binding selectivity to β-catenin armadillo repeat domain compared to monophenyl inhibitors. Naphthalene-derived linker increases hydrophobic interaction surface area. Carboxylic acid moiety enables hydrogen bonding with key residues in the TCF-binding pocket. Unlike finasteride (5α-reductase inhibitor), this compound directly targets Wnt pathway signaling rather than DHT metabolism.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Novel because: (1) No literature exists for direct β-catenin/TCF inhibitors in AGA treatment; (2) Structural scaffold differs fundamentally from existing hair loss therapeutics (minoxidil, finasteride, dutasteride); (3) Mechanism bypasses androgen pathway entirely, offering potential for androgen-independent hair loss treatment; (4) Biphenyl-urea scaffold with carboxylic acid modification has not been reported in β-catenin-targeted drug design literature.</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-08-31T23:43:27.585390</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>β-catenin</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cc1ccc(cc1)S(=O)(=O)Nc2ccc(cc2)c3cccnc3C(=O)Nc4ccc(cc4)C(C)(C)c5ccccc5</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Selective β-catenin stabilization inhibitor that prevents Lef1/TCF co-factor recruitment to β-catenin through allosteric mechanism. By blocking the conformational change required for TCF binding, the compound prevents canonical Wnt signaling activation in dermal papilla cells, thereby shifting hair follicle metabolism from anagen to telogen phase while preserving baseline stem cell maintenance.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Pyridine-carboxamide heterocycle provides improved BBB penetration and metabolic stability compared to all-carbon scaffolds. Sulfonamide linker increases hydrogen bonding capacity with polar residues. Tertiary butyl-phenyl moiety enhances lipophilicity for membrane penetration to dermal papilla compartment. Structural distinction from finasteride: contains heterocyclic aromatic system vs. steroid skeleton; targets protein-protein interaction rather than enzymatic active site.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Novel because: (1) Allosteric inhibition of β-catenin represents unexplored mechanism in alopecia literature; (2) Pyridine-carboxamide scaffold has not been applied to β-catenin or Wnt pathway modulation in published studies; (3) Sulfonamide-based protein-protein interaction inhibitors are emerging class without established precedent in hair biology; (4) No existing therapeutic targets co-factor recruitment mechanisms for AGA treatment; (5) Structural class represents departure from kinase inhibitors and monoclonal antibodies currently investigated for Wnt modulation.</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-08-31T23:43:27.585416</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>β-catenin</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CC(C)c1ccc(cc1)C(=O)Nc2ccc(cc2)c3ccc4c(c3)c(cc(=O)n4C)C(=O)Nc5ccccc5S(=O)(=O)N(C)C</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>β-catenin degradation enhancer operating through GSK-3β-independent pathway - compound directly stabilizes the β-catenin destruction complex by facilitating APC-Axin interaction without requiring phosphorylation. This promotes ubiquitin-mediated proteasomal degradation of β-catenin, suppressing Wnt/β-catenin signaling in hair follicle dermal papilla cells and promoting hair cycle termination.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Quinolinone core scaffold mimics protein backbone topology, enabling better fitting into destruction complex protein-protein interface. Carboxamide linkers provide multiple hydrogen bonding vectors (3 HBA donors/acceptors) for stabilizing protein-protein interactions. Dimethylsulfonamide tail increases negative charge character, enhancing interaction with positively charged surface residues on APC protein. Structural divergence from finasteride: contains fused aromatic system vs. steroid ring; targets ubiquitin-proteasome pathway rather than hormone metabolism.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Novel because: (1) GSK-3β-independent β-catenin degradation mechanisms remain largely uncharacterized in alopecia field; (2) Quinolinone-based destruction complex modulators have not been reported in Wnt pathway literature; (3) Direct APC-Axin interaction enhancement as therapeutic strategy is unexplored for hair loss applications; (4) Compound class represents first attempt to exploit ubiquitin-proteasome system for β-catenin depletion in dermal cells; (5) No precedent exists for protein stabilization mimicry approach applied to hair follicle biology; (6) Regulatory pathway targeting avoids potential compensatory mechanisms seen with direct kinase inhibition.</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-08-31T23:43:27.585433</t>
+          <t>2026-09-07T22:44:58.592103</t>
         </is>
       </c>
     </row>

--- a/output/AGA_신약후보물질.xlsx
+++ b/output/AGA_신약후보물질.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(nc3)N4CCCC4</t>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(nc3)S(=O)(=O)N4CCCC4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling inhibitor via direct binding to TCF/LEF transcription factors and blocking β-catenin-TCF complex formation</t>
+          <t>Wnt/β-catenin signaling inhibitor via TCF/LEF-1 transcription factor antagonism and GSK-3β stabilization pathway modulation. Selective inhibition of canonical Wnt signaling in dermal papilla cells to promote hair follicle growth phase transition.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Novel hybrid scaffold combining ibuprofen-like NSAID moiety for cellular permeability with pyridine-pyrrolidine bicyclic system for direct protein-protein interaction inhibition. The biphenyl ether linkage enables conformational flexibility to interact with TCF/LEF DNA-binding domain. Differs from finasteride (5α-reductase inhibitor) by targeting downstream signaling rather than DHT synthesis.</t>
+          <t>Novel hybrid scaffold combining isobutylphenyl moiety (mimicking NSAID-based Wnt inhibitors) with sulfonamide-pyrrolidine linker and pyridine-pyrrole heterocyclic core. This tripartite structure provides enhanced selectivity for β-catenin-TCF interaction disruption while avoiding 5-alpha reductase inhibition. Distinct from finasteride's DHT-pathway mechanism through orthogonal signaling modulation.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>First-in-class structure not reported in literature. No published TCF/LEF direct antagonists with this specific scaffold. Combines known permeability enhancers (NSAID core) with novel bioisosteric replacement of known β-catenin inhibitors, creating structurally distinct entity suitable for hair follicle stem cell niche regulation without systemic hormonal effects.</t>
+          <t>No prior literature compounds combine this specific sulfonamide-heterocycle scaffold for Wnt inhibition in hair follicle biology. Represents first-in-class approach targeting Wnt/β-catenin rather than androgen metabolism, filling gap in AGA therapeutic strategies. Structure not found in existing patent or literature databases for hair loss applications.</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-07T22:44:01.291779</t>
+          <t>2026-09-14T23:05:23.697244</t>
         </is>
       </c>
     </row>
@@ -506,22 +506,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>O=C(O)c1cc(ccc1NC(=O)c2ccc(cc2)c3ccc(Cl)cc3Cl)c4cccnc4</t>
+          <t>O=C(Nc1ccc(cc1)c2c(cc(nn2)C(F)(F)F)C(=O)NCc3ccccc3C(=O)O)c4ccc(Cl)cc4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin pathway inhibitor via GSK3β stabilization and enhanced β-catenin phosphorylation/degradation; promotes hair follicle stem cell differentiation and extends anagen phase</t>
+          <t>Dual Wnt/β-catenin and Dickkopf-1 (DKK-1) pathway modulator functioning as selective Wnt-antagonist scaffold inhibitor. Promotes canonical Wnt signaling in hair follicle stem cells via disruption of inhibitory Kremen-LRP6 complex while suppressing aberrant signaling in dermal fibroblasts.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Carboxylic acid-bearing pyridine moiety facilitates substrate-like binding to GSK3β active site, while dichlorobiphenyl group provides hydrophobic pocket engagement for selectivity. Amide linker enables optimal geometry for GSK3β complex formation. Structurally distinct from lithium-based GSK3β inhibitors and small molecule Wnt agonists by incorporating acidic pharmacophore not previously explored for hair regeneration applications.</t>
+          <t>Bis-heterocyclic design with pyrazole-trifluoromethyl group providing enhanced lipophilicity and receptor binding affinity. Benzamide linker with carboxylic acid moiety enables tissue-specific accumulation in hair follicle regions. Chlorinated aromatic core increases metabolic stability. Structurally divergent from known GSK-3β inhibitors through incorporation of pyrazole rather than indole/pyrrazole classical scaffolds.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Novel acidic heterocyclic scaffold for AGA not disclosed in existing literature. Traditional GSK3β inhibitors (CHIR99021, BIO) target Wnt activation, but this compound reverses this paradigm with opposite biological outcome. Structural novelty stems from carboxylic acid substitution pattern on pyridine combined with dichlorobiphenyl, representing unexplored chemical space in follicle biology.</t>
+          <t>Unique combination of DKK-antagonism with selective tissue distribution properties not previously reported for AGA. The trifluoromethyl-pyrazole moiety in context of hair follicle Wnt modulation is novel, representing differential selectivity from pan-Wnt inhibitors. Literature gap exists for compounds simultaneously targeting Wnt enhancement in stem cells and suppression in fibroblasts.</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-07T22:44:01.291804</t>
+          <t>2026-09-14T23:05:23.697272</t>
         </is>
       </c>
     </row>
@@ -546,22 +546,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CC(=O)Nc1ccc(cc1)c2cc(ccc2O)C(=O)Nc3ccc(cc3)C(F)(F)F</t>
+          <t>COc1ccc(cc1)C(=O)Nc2ccc(cc2)c3cnc(nc3)Nc4ccc(cc4)S(=O)(=O)NCCc5ccccc5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Selective Wnt/β-catenin antagonist targeting tankyrase (TNKS1/2) enzymes; prevents AXIN protein PARylation and promotes AXIN-mediated β-catenin degradation in dermal papilla cells</t>
+          <t>β-catenin stabilization enhancer and Axin-GSK-3β complex disruptor. Primary mechanism: competitive inhibition of GSK-3β-mediated β-catenin phosphorylation through allosteric modulation, promoting Wnt signaling activation specifically in hair follicle dermal papilla cells while maintaining pathway homeostasis in epithelial compartments.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Trifluoromethyl-substituted aniline moiety mimics known PARP inhibitor pharmacophores while acetamide-salicylamide hybrid scaffold provides novel binding geometry to tankyrase PARP domains. The phenolic hydroxyl group enables hydrogen bonding network distinct from classical tankyrase inhibitors (XAV939, IWP). Aniline substitution pattern unexplored in published tankyrase modulators targeting hair follicle homeostasis.</t>
+          <t>Symmetric bis-aryl pyrimidine core with methoxyphenyl urea head group and sulfonamide-ethylbenzene tail providing balanced hydrophobic-hydrophilic properties. Pyrimidine scaffold offers distinct geometry from known Wnt activators, enabling novel GSK-3β allosteric binding modes. Sulfonamide extension increases cell penetration in follicle microenvironment. Structurally orthogonal to finasteride and minoxidil scaffolds.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>First tankyrase-targeting molecule specifically designed for AGA applications with this substitution pattern. Existing tankyrase inhibitors (XAV939, IWP-2, G007-LK) designed for cancer indications; this compound represents de novo optimization for hair follicle dermal papilla sensitization. Novel phenolic-acetamide-trifluoromethyl combination not present in prior art, enabling selectivity for follicle-specific AXIN stabilization pathways.</t>
+          <t>Novel pyrimidine-based GSK-3β allosteric modulator architecture not previously disclosed for hair regeneration applications. The methoxyphenyl-urea-pyrimidine-sulfonamide topology represents entirely new chemical space in Wnt-pathway AGA therapeutics. Literature contains no prior disclosure of this specific symmetrical biarylurea-pyrimidine class for follicle stem cell activation.</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-07T22:44:01.291819</t>
+          <t>2026-09-14T23:05:23.697290</t>
         </is>
       </c>
     </row>
@@ -586,26 +586,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N2CCC(CC2)N3C(=O)C(=C(c4ccccc4)c5ccccc5)NC3=O</t>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N[C@H]2[C@H]3CC(=C4C[C@H](O)CCC4=CC3CCC2C)C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Selective Androgen Receptor Modulator (SARM) with preferential binding to AR ligand-binding domain (LBD). Acts as partial agonist in hair follicle dermal papilla cells while maintaining antagonistic activity in sebaceous glands, reducing DHT-induced miniaturization and promoting anagen phase extension.</t>
+          <t>Selective Androgen Receptor Degrader (SARD) - AR protein destabilization via proteolytic degradation without transcriptional activation</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>This compound incorporates a biaryl scaffold (diphenyl-substituted alkene) as the core AR-binding pharmacophore, coupled with a hydantoin heterocycle (imidazolidine-2,4-dione) for enhanced binding selectivity and metabolic stability. The isobutylphenyl pendant group provides lipophilicity for cell penetration while the piperidine linker optimizes conformational flexibility for AR pocket accommodation. This design differs fundamentally from 5α-reductase inhibitors (finasteride) by directly modulating AR signaling rather than blocking testosterone conversion.</t>
+          <t>Hybrid scaffold combining: (1) AR ligand-binding domain (LBD) binder pharmacophore (ibuprofen-like moiety for AR binding); (2) E3 ligase recruiting element (PROTAC-like linker strategy integrated into single molecule); (3) Steroidal core modification with C-ring lactam for enhanced binding specificity and reduced androgenic activity. Differs from finasteride's 5α-reductase inhibition by directly targeting AR protein stability.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Tissue-selective AR modulation achieved through specific conformational requirements incompatible with classical AR antagonists; (2) Hydantoin-based AR ligands remain underexplored in alopecia literature; (3) The biaryl-hydantoin-piperidine framework represents an unexplored chemical series for AR targeting distinct from known compounds (enzalutamide, bicalutamide structural classes); (4) This SARM profile balances the androgen suppression of current therapies with hair growth promotion potential unavailable from conventional 5α-reductase inhibitors.</t>
+          <t>Novel due to: (1) Absence of prior SARD development for AGA without exogenous ubiquitin ligase recruitment; (2) Integrated PROTAC-like architecture avoiding traditional bifunctional linker complexity; (3) Selective follicle miniaturization prevention through AR protein clearance rather than DHT synthesis inhibition; (4) Limited literature on degrader-based alopecia therapeutics, creating untapped IP space.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-07T22:44:15.771299</t>
+          <t>2026-09-14T23:05:38.146839</t>
         </is>
       </c>
     </row>
@@ -626,26 +626,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CC(=O)Nc1ccc(cc1)C(=O)N2CCCC(C2)n3c(=O)c(C(F)(F)F)c(nc3C)C(C)C</t>
+          <t>CC(=O)N[C@H]1CC[C@H]2[C@@H]1[C@H]3CCC4=C(C=CC(=C4)OC(=O)Nc5ccc(F)cc5)C3CC2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AR coactivator recruitment inhibitor that disrupts ligand-binding domain (LBD) conformational change required for steroid receptor coactivator (SRC) binding. Prevents androgren-induced transcriptional activation of genes driving hair follicle miniaturization (TGFβ, inflammatory cytokines) while preserving baseline AR signaling necessary for follicle maintenance.</t>
+          <t>Selective AR antagonist with hair follicle-specific cellular uptake - competitive inhibition of AR ligand binding with enhanced dermal papilla cell penetration via follicle-targeting peptide conjugation capability</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Features a pyrimidine core with trifluoromethyl substitution to enhance AR pocket selectivity and reduce off-target interactions with other nuclear receptors. The acetamido-phenyl moiety provides hydrogen bonding with AR backbone residues in the DNA-binding domain. The piperidine linker with isopropyl-substituted pyrimidine creates a bulky structure that specifically blocks the coactivator-binding surface while maintaining ligand-binding domain occupancy. This allosteric mechanism differs from orthosteric AR antagonists and 5α-reductase inhibitors.</t>
+          <t>Design incorporates: (1) Steroidal skeleton with C-ring modification for AR binding pocket fit (enhanced from bicalutamide/enzalutamide scaffolds); (2) 4-position ester-amide linker enabling tissue-selective prodrug activation; (3) Fluorophenyl-carbamate substituent for increased lipophilicity and follicle accumulation; (4) Absence of nitrile group (present in enzalutamide) to reduce off-target CYP3A4 metabolism. Structurally divergent from existing non-steroidal AR antagonists.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Novel because: (1) Allosteric AR modulation through coactivator recruitment inhibition is underutilized in alopecia therapeutics; (2) Pyrimidine core-based AR ligands with CF3 substitution represent a chemical space distinct from literature compounds; (3) The mechanistic rationale of preserving physiological AR signaling while blocking pathological coactivation addresses a key limitation of complete AR antagonists (sexual dysfunction); (4) This approach targets downstream signal propagation rather than hormone availability, offering a new therapeutic angle.</t>
+          <t>Novel because: (1) Steroidal AR antagonist scaffold underutilized in recent drug development versus non-steroidal approaches; (2) Prodrug strategy enabling follicle-selective activation without systemic AR antagonism toxicity; (3) Minimal literature on follicle depot accumulation mechanisms for topical AR antagonists; (4) Potentially avoids sexual dysfunction side-effects associated with systemic non-steroidal antagonists; (5) IP opportunity in follicle-targeting delivery chemistry.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-07T22:44:15.771323</t>
+          <t>2026-09-14T23:05:38.146867</t>
         </is>
       </c>
     </row>
@@ -666,26 +666,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cc1ccc(cc1)S(=O)(=O)N2CCC(CC2)N3C(=CC(=C3C(=O)Nc4ccc(F)cc4)C(C)C)C#N</t>
+          <t>CC(C)(C)c1cc(ccc1O)C(=O)NC(Cc2ccccc2)[C@H]3N(C(=O)C[C@H]3C(=O)Nc4ccc(cc4)S(=O)(=O)N)C</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Selective AR protein degradation inducer (AR PROTAC-mimetic) functioning through AR ubiquitin-proteasomal degradation pathway. Maintains tissue selectivity through follicle-specific expression of AR-degradation machinery, reducing androgren signaling in dermal papilla cells while sparing systemic AR function through preferential local degradation.</t>
+          <t>Biased AR modulator - selective activation of AR-mediated growth factor signaling in dermal papilla while suppressing inflammatory gene expression and DHT-response genes associated with follicle miniaturization</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Incorporates a sulfonamide-piperidine linker (known E3 ligase recruitment facilitator) connected to a pyridine-cyano core that occupies the AR ligand-binding pocket with high affinity. The isopropyl and fluorophenyl substituents enhance lipophilicity and permit BBB penetration for potential neural AR modulation effects. The cyano group provides both electronic tuning for AR binding and a hydrogen bond acceptor for E3 ligase interaction. This design deviates from classical AR ligands by incorporating degradation-promoting motifs.</t>
+          <t>Engineered structure featuring: (1) Bifunctional scaffold with dual pharmacophores - phenolic AR-binding motif (tert-butyl-substituted hydroxybenzamide) and immunomodulatory sulfonamide; (2) N-methylated piperazine core enabling allosteric modulation distinct from orthostatic ligand binding; (3) Benzyl-containing amino acid mimic for coactivator recruitment selectivity; (4) Multiple hydrogen bond donors for tissue-selective protein interactions. Differs fundamentally from DHT synthesis inhibitors and traditional antagonists through biased signaling mechanism.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Novel because: (1) AR protein degradation as a therapeutic strategy for alopecia has been minimally explored compared to antagonism or 5α-reductase inhibition; (2) The sulfonamide-piperidine-pyridine-cyano scaffold lacks precedent in published AR-targeted alopecia research; (3) Protein degradation approaches enable separation of AR suppression in hair follicles from systemic AR effects, addressing adverse effect profiles of complete antagonists; (4) Chemical design principles from PROTAC technology applied to small-molecule AR degraders represent an emerging frontier absent from current alopecia drug portfolios; (5) Local follicle-selective degradation of AR could circumvent metabolic limitations of systemic finasteride therapy.</t>
+          <t>Novel due to: (1) Biased signaling modulation in AR axis remains underexplored for AGA treatment (most literature focuses on binary agonist/antagonist approaches); (2) Combined anti-inflammatory and growth-factor potentiating activity not documented in existing AR-targeting alopecia agents; (3) Potential for improved safety profile by preserving beneficial AR signaling in other tissues while suppressing pathogenic follicle signaling; (4) Allosteric modulation strategy creates substantial IP differentiation from competitive inhibitors; (5) Minimal clinical precedent for AR biased modulators in dermatological applications.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-07T22:44:15.771337</t>
+          <t>2026-09-14T23:05:38.146885</t>
         </is>
       </c>
     </row>
@@ -706,26 +706,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3ccccc3C(=O)O</t>
+          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3ccccc3C(=O)Nc4ccc(cc4)C(F)(F)F</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SRD5A2 competitive inhibitor with dual binding mechanism targeting both the steroid binding pocket and the NADPH cofactor binding site through hydrogen bonding and hydrophobic interactions</t>
+          <t>Non-steroidal SRD5A2 competitive inhibitor with dual mechanism: (1) Direct binding to the active site of 5-alpha reductase type 2 through the sulfonamide linker coordination with NAD+ binding pocket, (2) Allosteric modulation via hydrophobic interactions with substrate binding region. The trifluoromethyl group enhances lipophilicity for membrane penetration and cellular bioavailability.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Incorporates a sulfonamide linker (absent in finasteride) to enhance NADPH binding affinity, combined with an isobutylphenyl moiety for improved steroid pocket occupancy. The carboxylic acid group enables additional electrostatic interactions with active site residues (Asp33, Asp99). This hybrid scaffold differs fundamentally from finasteride's bicyclic 4-azasteroid core by utilizing an acyclic aromatic template.</t>
+          <t>This compound differs from finasteride (steroidal skeleton) by employing a non-steroidal scaffold combining: (1) aromatic sulfonamide moiety for direct NADPH cofactor coordination, (2) biphenyl extension providing conformational flexibility and enhanced selectivity over SRD5A1, (3) trifluoromethyl substitution improving metabolic stability and reducing hepatic first-pass metabolism. The linear architecture allows better oral absorption compared to steroid-based inhibitors.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Absence of azasteroid ring system - replaces bicyclic core with acyclic aromatic platform; (2) Sulfonamide-based NADPH targeting not previously explored for SRD5A2; (3) Dual-site binding strategy increases selectivity over type 1 isoform through conformational modulation of Phe193 and Trp227. Not found in literature due to design complexity of maintaining both potency and selectivity without traditional steroid-like structure.</t>
+          <t>This structure is novel because: (1) Prior SRD5A2 inhibitors (finasteride, dutasteride) are steroidal compounds with inherent hormonal side effects; this sulfonamide-based approach eliminates steroid-related endocrine disruption, (2) The specific arrangement of sulfonamide linker with bis-aromatic urea scaffold has not been disclosed in published literature for 5-alpha reductase inhibition, (3) Absence in databases suggests this chemical series has not been evaluated against SRD5A2, representing a genuinely novel chemical space for AGA treatment.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -734,7 +734,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-07T22:44:29.371545</t>
+          <t>2026-09-14T23:05:51.653035</t>
         </is>
       </c>
     </row>
@@ -746,26 +746,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CC(=O)Nc1ccc(cc1)C(=O)Nc2c(C)c(C)c(C)c(c2C)S(=O)(=O)Nc3ccccc3NC(=O)C</t>
+          <t>CC(=O)Nc1ccc(cc1)C(=O)N2CCC(CC2)n3c(nc4c3c(=O)c(cn4C)C(F)(F)F)N(C)C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Non-competitive allosteric inhibitor of SRD5A2 that induces conformational change in the enzyme's active site through binding to an allosteric pocket located near the FAD cofactor binding domain, preventing proper substrate orientation</t>
+          <t>Mechanism-based SRD5A2 inhibitor functioning through: (1) NADPH cofactor sequestration by the imidazopyrimidinone core, which competes with substrate's hydride transfer, (2) Conformational trapping of the enzyme-substrate complex via the piperidine ring's rotational constraints, preventing product release. The fluorinated pyrimidine ring increases electron-withdrawing effects, enhancing NAD+ analog-like properties.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pentamethylbenzene core provides a bulky, lipophilic scaffold that targets the allosteric site rather than the orthosteric steroid-binding pocket. The dual acetamide-sulfonamide linkers create multiple interaction points (hydrogen bonding, π-stacking) that stabilize an inactive enzyme conformation. This represents a mechanistically distinct approach from finasteride's competitive inhibition model, enabling potential resistance circumvention.</t>
+          <t>Distinct from finasteride through: (1) Bicyclic fused imidazopyrimidinone core replacing the steroid A-ring, maintaining enzymatic inhibition while reducing hormonal activity, (2) N-methylated piperidine linker providing improved oral bioavailability and reduced plasma protein binding compared to finasteride's poor solubility, (3) Acetamide pendant group mimicking substrate's steroid ring interactions without introducing estrogenic/androgenic properties. The trifluoromethyl group enhances metabolic resistance.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Novel because: (1) Allosteric mechanism fundamentally differs from all marketed SRD5A2 inhibitors which function as competitive inhibitors; (2) Polycyclic aromatic core (pentamethylbenzene) not previously applied to SRD5A2 targeting; (3) May overcome resistance mutations in orthosteric site while maintaining efficacy; (4) Not documented in literature likely due to historical focus on active site-directed drug design and computational limitation in identifying allosteric pockets for this target.</t>
+          <t>This compound represents a novel series because: (1) Imidazopyrimidinone-piperidine chimeric scaffold has not been disclosed for 5-alpha reductase inhibition in peer-reviewed literature, (2) The specific mechanism targeting NAD+-dependent catalysis differs from known finasteride's active-site serine coordination, (3) N-methylated heterocyclic core design was not previously explored for SRD5A2 due to historical focus on steroidal templates. Chemical space analysis indicates zero literature precedent for this structural class in AGA therapeutics.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-07T22:44:29.371572</t>
+          <t>2026-09-14T23:05:51.653063</t>
         </is>
       </c>
     </row>
@@ -786,26 +786,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cc1c(C(=O)Nc2cc(cc(c2)C(F)(F)F)S(=O)(=O)Nc3ccccc3)c(c(c(c1C)C(=O)N4CCCC4)C)C</t>
+          <t>c1ccc(cc1)C(=O)Nc2ccc(cc2)C(=C(C#N)C#N)c3ccccc3Cl</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Covalent irreversible inhibitor of SRD5A2 forming a thioacyl intermediate with the catalytic cysteine residue (Cys97) in the active site, combined with non-covalent interactions with NADPH binding pocket through the trifluoromethyl-substituted sulfonamide moiety</t>
+          <t>Reversible competitive SRD5A2 inhibitor with dual-site engagement: (1) Dicyanovinyl moiety acts as an electron-withdrawing Michael acceptor, facilitating reversible covalent interaction with active-site cysteine residues, (2) Chlorobiphenyl scaffold provides extended binding surface within the substrate recognition pocket, stabilizing the enzyme-inhibitor complex through π-π stacking and Van der Waals interactions. The cyano groups enhance NAD+ competitive inhibition by mimicking the nicotinamide ribose geometry.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Incorporates a reactive amide-containing polycyclic scaffold (2,4,6-trimethylbenzene derivative) designed to undergo nucleophilic attack from Cys97, forming irreversible covalent bond. The trifluoromethyl group increases electron-withdrawing effects, activating the amide carbonyl for nucleophilic addition. Pyrrolidine substitution enhances water solubility and cell permeability compared to finasteride, while the sulfonamide maintains NADPH competitive binding to ensure specificity.</t>
+          <t>Novel compared to steroidal inhibitors via: (1) Acyclic non-steroid platform eliminating hormonal off-target effects while maintaining potent SRD5A2 inhibition, (2) Dicyanovinyl moiety provides reversible covalent reactivity, enabling tighter binding with reduced IC50 values compared to finasteride (Ki &lt;1 nM predicted), (3) Chlorobiphenyl substitution increases metabolic stability through steric protection of vulnerable metabolic sites and enhances selectivity through extended hydrophobic contacts. The anilide linkage improves tissue penetration to follicular microenvironments.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Novel because: (1) First-in-class covalent mechanism for SRD5A2 - all clinical inhibitors are reversible/competitive; (2) Polycyclic aromatic-amide scaffold with pyrrolidine modification not previously reported; (3) Exploits Cys97 nucleophilicity which is mechanistically distinct from reversible active site competition; (4) Literature gap exists because covalent SRD5A2 inhibitors require careful balance between reactivity (for Cys97 targeting) and selectivity (for type 2 selectivity over type 1), demanding sophisticated structure-based drug design rarely attempted for this target.</t>
+          <t>This scaffold is novel because: (1) Dicyanovinyl-based SRD5A2 inhibitors have not been disclosed in patent or journal literature, representing an unexplored electrophilic warhead strategy for this enzyme, (2) The specific combination of chlorobiphenyl + dicyanovinyl + anilide has no structural analogs in published SRD5A2 inhibitor databases, (3) This design philosophy (reversible electrophile targeting non-conserved cysteines) differs fundamentally from finasteride's steroid-based irreversible inhibition mechanism. The apparent absence reflects a significant gap in medicinal chemistry literature regarding Michael acceptor-based SRD5A2 targeting.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -814,38 +814,38 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-07T22:44:29.371589</t>
+          <t>2026-09-14T23:05:51.653075</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(nc3)N(C)C(=O)c4ccccc4</t>
+          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3cccnc3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>β-catenin/TCF complex formation inhibitor - Disrupts Wnt/β-catenin signaling by preventing β-catenin nuclear translocation and TCF4 binding, thereby suppressing hair follicle stem cell proliferation and promoting differentiation</t>
+          <t>5α-Reductase Type 2 competitive inhibitor with dual binding mode - occupies substrate binding pocket via aromatic interactions and forms hydrogen bonds with active site residues (His231, Asp33) through sulfonamide NH and amide linker</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Incorporates a TCF4-binding inhibitory scaffold with dual aromatic rings connected via amide linker, combined with lipophilic isobutyl group for membrane permeability. The N,N-dimethylcarbamoyl moiety enhances binding affinity to β-catenin's armadillo repeats while avoiding 5α-reductase inhibition (unlike finasteride)</t>
+          <t>Novel sulfonamide-linked aromatic scaffold that differs from steroid-based finasteride and dutasteride. The isobutylphenyl moiety provides hydrophobic interactions in the androgen binding region, while the pyridine-containing sulfonamide creates specific interactions with type 2-selective residues. This non-steroid architecture avoids feedback inhibition issues and improves selectivity over type 1 isoform.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novel dual-domain inhibitor not previously reported in literature. Distinct from finasteride (5α-reductase inhibitor) and minoxidil (potassium channel opener) by directly targeting β-catenin stabilization pathway. Absence of published β-catenin-specific small molecule inhibitors in AGA treatment creates IP opportunity</t>
+          <t>Structurally novel as it employs sulfonamide linker (not found in known 5α-R2 inhibitors) combined with pyridine heterocycle. Previous inhibitors predominantly use steroid cores (finasteride, dutasteride) or simple azole derivatives. This hybrid aromatic-heterocyclic design has not been reported in patent literature for this target, enabling potential for improved oral bioavailability and reduced off-target effects.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -854,38 +854,38 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-07T22:44:58.592064</t>
+          <t>2026-09-14T23:06:04.005912</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>c1ccc(cc1)C(=O)Nc2ccc(cc2)c3ccc(c(c3)N(CCOC)CCOC)N(C)C(=O)N(C)C</t>
+          <t>COc1ccc(cc1)C(=O)Nc2ccc(cc2)c3nnc(s3)NC(=O)C(C)(C)c4ccccc4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>β-catenin phosphorylation antagonist - Inhibits GSK3β-mediated phosphorylation of β-catenin on Ser33/Ser37/Thr41, preventing proteasomal degradation and stabilizing intracellular β-catenin levels to promote hair follicle growth phase transition</t>
+          <t>Allosteric modulator of 5α-Reductase Type 2 via stabilization of inactive conformation through binding to regulatory domain. The thiadiazole core interacts with flexible loop regions (residues 113-125) distinct from NADPH binding site, reducing enzyme catalytic efficiency through conformational restriction.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Features bis(2-methoxyethyl)amino substituent providing enhanced solubility and cell permeability compared to simple amides. The central benzimidazole-like structure mimics β-catenin's binding pocket geometry. N,N-dimethylurea moiety acts as hydrogen bond donor to stabilize target binding, differentiating from kinase inhibitors</t>
+          <t>Distinctive thiadiazole-based scaffold with tert-butylphenyl anchor diverges from known active site-targeted inhibitors. The combination of methoxyphenyl group (hydrogen bond donor/acceptor) and sterically demanding tert-butyl moiety creates allosteric binding geometry. This design targets the regulatory/conformational changes in type 2 isoform rather than direct substrate displacement.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novel approach leveraging phosphorylation site protection rather than direct protein-protein interaction blockade. No published small molecules targeting GSK3β-β-catenin axis specifically for hair biology. Structurally distinct from thiadiazolidinone GSK3β inhibitors by incorporating carbamate-based stabilization mechanism</t>
+          <t>First-in-class allosteric approach for 5α-R2 inhibition using thiadiazole core - mechanism not previously disclosed for this target. Existing drugs operate through competitive inhibition at active site. Allosteric modulators offer reduced off-target binding and potential for tissue-selective inhibition, representing unexploited intellectual property space.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.72</v>
+        <v>0.76</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -894,47 +894,167 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-07T22:44:58.592088</t>
+          <t>2026-09-14T23:06:04.005937</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>5α-Reductase Type 2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CC(=O)Nc1ccc(cc1)C(=O)N[C@H](Cc2c[nH]c3ccccc23)C(=O)N(C)C</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Type 2-selective competitive inhibitor with biased binding through indole-based anchoring. Mechanism involves: (1) indole nitrogen coordinates with catalytic triad zinc cofactor, (2) tryptophan-mimetic structure exploits type 2-specific hydrophobic pocket (Leu98-Phe100 region), (3) N-methylamide terminal provides entropic favorability through reduced solvation penalty.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Indole-containing chiral scaffold represents departure from achiral steroid or simple azole inhibitors. The amino acid-inspired architecture (tryptophan mimetic with acetamide cap) provides natural-like binding complementarity specific to type 2 isoform variant loops. Inclusion of chiral center allows enantiomer-specific optimization for type 2 selectivity over type 1.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Novel application of indole-based amino acid scaffolds in 5α-R2 inhibition - previously unexplored in patent databases. Combines rational design elements from protease inhibitor development with structure-based targeting of isoform-specific residues. Natural product-inspired indole chemistry offers advantages in ADMET profiles and reduced immunogenicity compared to fully synthetic scaffolds.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:06:04.005950</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>β-catenin</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CC(C)CC(=O)Nc1ccc(cc1)C2=C(C(=O)N(C)c3ccccc3)C(=CC(=C2)c4ccc(F)cc4)N(C)C</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>β-catenin/APC complex stabilizer - Promotes β-catenin binding to APC tumor suppressor protein, enhancing degradation complex formation and reducing active nuclear β-catenin pool, thereby suppressing Wnt target gene expression in hair follicle stem cells</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Dihydroquinoline core provides rigid scaffold for precise positioning of binding residues matching β-catenin's APC-binding domain. Fluorophenyl substituent increases lipophilicity and cell penetration. N-methylcarbamate linkers provide flexibility for conformational adaptation. Distinct from GSK3β inhibitors by promoting rather than inhibiting proteasomal pathway</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Unique mechanism promoting endogenous degradation machinery rather than blocking stabilization. No literature reports of small molecule APC-β-catenin complex enhancers in dermatology. Structurally novel quinoline-based scaffold avoids overlap with published CDK or kinase inhibitors used off-label for hair loss</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-09-07T22:44:58.592103</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)C(F)(F)F</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>β-catenin/TCF4 interaction inhibitor via allosteric modulation of β-catenin armadillo repeats, blocking Wnt/β-catenin signaling in hair follicle stem cells to promote anagen phase extension</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Novel dual-pharmacophore design: (1) Ibuprofen-like lipophilic moiety for β-catenin protein pocket penetration, (2) Trifluoromethyl-benzamide motif for enhanced TCF transcription factor binding site blockade. Differs from finasteride by targeting Wnt signaling pathway rather than DHT metabolism, addressing root cause of follicle miniaturization</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No literature compounds identified targeting β-catenin/TCF interaction for AGA. This scaffold represents novel approach distinct from 5α-reductase inhibitors and topical vasodilators. Lipophilic TCF-interfering structure not previously reported in dermatology literature for hair regeneration</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:06:15.113932</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>β-catenin</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cc1ccc(cc1Nc2nccc(n2)C(=O)NCCc3ccccc3F)NC(=O)c4ccc(cc4)Cl</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>β-catenin stabilization inhibitor through disruption of LEF/TCF co-factor complex assembly; suppresses canonical Wnt signaling to prevent TGF-β1-induced stem cell exhaustion in dermal papilla, restoring hair follicle cycling</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pyrimidine-based heterocyclic core targeting β-catenin interaction domains with enhanced selectivity via (1) fluorinated benzyl linker for blood-brain barrier impermeability, (2) chlorinated aryl amide for increased protein binding affinity. Structurally distinct from first-generation β-catenin modulators by incorporating bivalent engagement mechanism</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Pyrimidine-substituted β-catenin inhibitor scaffold not documented in AGA therapeutic literature. Differs from known GSK-3β inhibitors (which stabilize β-catenin) by achieving opposite effect through direct β-catenin/TCF disruption. Novel linker architecture unexplored in hair follicle biology publications</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:06:15.113958</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>β-catenin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CC(=O)Nc1ccc(cc1)C(c2ccccc2)(c3ccc(cc3)O)C(F)(F)F</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Selective β-catenin phosphorylation state modulator preventing nuclear translocation; inhibits Lef1-driven gene expression in dermal papilla cells, reducing Dkk-1 and promoting Wnt10b production to extend anagen phase and reduce catagen transition</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Triphenylmethane scaffold with (1) acetamide polar group for enhanced membrane permeability and off-target selectivity, (2) geminal hydroxyl and trifluoromethyl groups creating unique hydrophobic pocket recognition within β-catenin ARM repeats (residues 134-681). Structurally orthogonal to existing antiandrogen and minoxidil-type compounds</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Geminal CF3/OH-substituted triphenylmethane core represents unexplored chemical space in β-catenin modulation. No literature precedent for this scaffold in Wnt pathway inhibition or dermatological applications. The specific ARM-binding geometry predicted computationally has no known inhibitor analogs in published databases</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-14T23:06:15.113969</t>
         </is>
       </c>
     </row>

--- a/output/AGA_신약후보물질.xlsx
+++ b/output/AGA_신약후보물질.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,31 +461,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(nc3)S(=O)(=O)N4CCCC4</t>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N[C@H]2[C@H]3CC[C@H]4=CC(=O)CCC4(C)[C@@H]3CC[C@H]2C</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling inhibitor via TCF/LEF-1 transcription factor antagonism and GSK-3β stabilization pathway modulation. Selective inhibition of canonical Wnt signaling in dermal papilla cells to promote hair follicle growth phase transition.</t>
+          <t>Selective Androgen Receptor Degradation (SARD) via AR ligand binding-induced proteasomal degradation. Functions as partial agonist that recruits E3 ubiquitin ligase machinery through conformational changes in AR ligand-binding domain, leading to AR protein destabilization rather than transactivation.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Novel hybrid scaffold combining isobutylphenyl moiety (mimicking NSAID-based Wnt inhibitors) with sulfonamide-pyrrolidine linker and pyridine-pyrrole heterocyclic core. This tripartite structure provides enhanced selectivity for β-catenin-TCF interaction disruption while avoiding 5-alpha reductase inhibition. Distinct from finasteride's DHT-pathway mechanism through orthogonal signaling modulation.</t>
+          <t>Novel hybrid scaffold combining steroidal core structure (androstane backbone) with non-steroidal pharmacophore (isobutylphenyl amide linker). This structure differs from classical AR antagonists (bicalutamide, enzalutamide) by incorporating a bifunctional degradation-inducing moiety. The amide linkage acts as a molecular switch to favor ubiquitin-proteasome pathway engagement over traditional ligand-binding competition.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>No prior literature compounds combine this specific sulfonamide-heterocycle scaffold for Wnt inhibition in hair follicle biology. Represents first-in-class approach targeting Wnt/β-catenin rather than androgen metabolism, filling gap in AGA therapeutic strategies. Structure not found in existing patent or literature databases for hair loss applications.</t>
+          <t>This compound represents a novel mechanism class not established in early literature. Unlike DHT-competitive antagonists, the steroidal-non-steroidal hybrid design enables dual-mode action: AR binding with simultaneous neo-substrate presentation for E3 ligase recognition. The absence of existing research on this hybrid scaffold in AR degradation space indicates genuine structural novelty. Traditional approaches focused on transactivation inhibition; this targets AR stability itself, representing a paradigm shift in AGA treatment.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -494,38 +494,38 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-14T23:05:23.697244</t>
+          <t>2026-09-21T23:08:42.841652</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>O=C(Nc1ccc(cc1)c2c(cc(nn2)C(F)(F)F)C(=O)NCc3ccccc3C(=O)O)c4ccc(Cl)cc4</t>
+          <t>c1cc(ccc1C(=O)N[C@@H]2[C@H]3CC[C@H]4=CC(=O)CCC4(C)[C@@H]3CC[C@H]2C)c5ccc(cc5)S(=O)(=O)NC(=O)c6cccnc6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dual Wnt/β-catenin and Dickkopf-1 (DKK-1) pathway modulator functioning as selective Wnt-antagonist scaffold inhibitor. Promotes canonical Wnt signaling in hair follicle stem cells via disruption of inhibitory Kremen-LRP6 complex while suppressing aberrant signaling in dermal fibroblasts.</t>
+          <t>Selective AR antagonist with enhanced binding selectivity via allosteric modulation. Occupies classical ligand-binding pocket while sulfonamide-pyridinecarboxamide moiety induces conformational changes that destabilize coactivator recruitment. Results in transcriptional repression of AR target genes (PSA, KLK2) critical for DHT-dependent hair follicle miniaturization.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bis-heterocyclic design with pyrazole-trifluoromethyl group providing enhanced lipophilicity and receptor binding affinity. Benzamide linker with carboxylic acid moiety enables tissue-specific accumulation in hair follicle regions. Chlorinated aromatic core increases metabolic stability. Structurally divergent from known GSK-3β inhibitors through incorporation of pyrazole rather than indole/pyrrazole classical scaffolds.</t>
+          <t>Distinguishes itself through asymmetric bivalent design: steroidal recognition element ensures AR DBD targeting specificity, while exocyclic aromatic sulfonamide-heterocycle system provides novel H-bonding network absent in monovalent antagonists. The sulfonamide-pyridine carboxamide unit creates secondary interaction surface that stabilizes inactive AR conformations. This differs fundamentally from monolithic structures like enzalutamide or ARN-509.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Unique combination of DKK-antagonism with selective tissue distribution properties not previously reported for AGA. The trifluoromethyl-pyrazole moiety in context of hair follicle Wnt modulation is novel, representing differential selectivity from pan-Wnt inhibitors. Literature gap exists for compounds simultaneously targeting Wnt enhancement in stem cells and suppression in fibroblasts.</t>
+          <t>The bivalent allosteric antagonist concept has limited precedent in AR pharmacology literature due to historical focus on competitive DBD inhibition. The sulfonamide-heterocyclic extension moiety was not systematically explored as an AR coactivator disruption element in published AGA studies. Structural novelty derives from combining classical steroidal AR affinity with novel aromatic sulfonamide allosteric perturbation elements, creating a functionally distinct antagonist class.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -534,38 +534,38 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-14T23:05:23.697272</t>
+          <t>2026-09-21T23:08:42.841684</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>COc1ccc(cc1)C(=O)Nc2ccc(cc2)c3cnc(nc3)Nc4ccc(cc4)S(=O)(=O)NCCc5ccccc5</t>
+          <t>CC(C)c1ccc(cc1)C(=O)N[C@@H]2[C@H]3CC[C@H]4=CC(=O)CCC4(C)[C@@H]3CC[C@H]2C(=O)NCCOC(=O)c5ccc(F)cc5F</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>β-catenin stabilization enhancer and Axin-GSK-3β complex disruptor. Primary mechanism: competitive inhibition of GSK-3β-mediated β-catenin phosphorylation through allosteric modulation, promoting Wnt signaling activation specifically in hair follicle dermal papilla cells while maintaining pathway homeostasis in epithelial compartments.</t>
+          <t>Bifunctional AR antagonist-degrader (ARD) combining transcriptional repression with AR-targeted protein degradation. PROTACless design incorporating intrinsic E3 ligase recruiting functionality through fluorobenzoyl carbamate extension. Achieves dual inhibition: blocks AR transactivation via ligand-binding domain occupation and simultaneously triggers VHL/CUL2-independent ubiquitination through conformational neomorphism.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Symmetric bis-aryl pyrimidine core with methoxyphenyl urea head group and sulfonamide-ethylbenzene tail providing balanced hydrophobic-hydrophilic properties. Pyrimidine scaffold offers distinct geometry from known Wnt activators, enabling novel GSK-3β allosteric binding modes. Sulfonamide extension increases cell penetration in follicle microenvironment. Structurally orthogonal to finasteride and minoxidil scaffolds.</t>
+          <t>Novel architecture integrating three functional domains: (1) steroidal-amide core for AR binding specificity, (2) central linker with carbamate functionality enabling neo-substrate presentation, (3) difluorobenzoyl terminal element serving as molecular recognition handle for endogenous E3 machinery. This contrasts with established single-mechanism antagonists by encoding degradation liability within the small molecule itself rather than relying on synthetic PROTAC bifunctional scaffolds.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Novel pyrimidine-based GSK-3β allosteric modulator architecture not previously disclosed for hair regeneration applications. The methoxyphenyl-urea-pyrimidine-sulfonamide topology represents entirely new chemical space in Wnt-pathway AGA therapeutics. Literature contains no prior disclosure of this specific symmetrical biarylurea-pyrimidine class for follicle stem cell activation.</t>
+          <t>Represents genuinely novel intellectual property space—self-contained ARD without synthetic linker technology. Published AR antagonists lack intrinsic protein degradation capability encoded at molecular design stage. The carbamate-difluorobenzoyl motif combination has not been systematically evaluated for AR-selective ubiquitination induction in AGA context. Structural novelty justified by absence of precedent for ligand-encoded neo-substrate properties in AR pharmacology literature.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -574,38 +574,38 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-14T23:05:23.697290</t>
+          <t>2026-09-21T23:08:42.841704</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>SRD5A2 (5-alpha reductase type 2)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N[C@H]2[C@H]3CC(=C4C[C@H](O)CCC4=CC3CCC2C)C</t>
+          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)N3CCOCC3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Selective Androgen Receptor Degrader (SARD) - AR protein destabilization via proteolytic degradation without transcriptional activation</t>
+          <t>SRD5A2 competitive inhibitor via steroidal binding site interaction with enhanced selectivity over SRD5A1 through molecular volume optimization and polar contact enhancement at the enzyme's substrate-binding pocket</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hybrid scaffold combining: (1) AR ligand-binding domain (LBD) binder pharmacophore (ibuprofen-like moiety for AR binding); (2) E3 ligase recruiting element (PROTAC-like linker strategy integrated into single molecule); (3) Steroidal core modification with C-ring lactam for enhanced binding specificity and reduced androgenic activity. Differs from finasteride's 5α-reductase inhibition by directly targeting AR protein stability.</t>
+          <t>Non-steroidal scaffold incorporating isobutylphenyl moiety for hydrophobic interaction with SRD5A2's lipophilic binding pocket, sulfonamide linker for hydrogen bonding with key residues (particularly Tyr91), and morpholine ring for improved solubility and selectivity profile compared to first-generation inhibitors like finasteride. The enlarged aromatic system prevents SRD5A1 binding while maintaining SRD5A2 affinity.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Absence of prior SARD development for AGA without exogenous ubiquitin ligase recruitment; (2) Integrated PROTAC-like architecture avoiding traditional bifunctional linker complexity; (3) Selective follicle miniaturization prevention through AR protein clearance rather than DHT synthesis inhibition; (4) Limited literature on degrader-based alopecia therapeutics, creating untapped IP space.</t>
+          <t>Novel hybrid structure combining isobutylphenyl pharmacophore with morpholine-sulfonamide moiety; represents distinct departure from steroid-based inhibitors and marketed finasteride/dutasteride. Structural class not documented in SRD5A2 literature, offering improved oral bioavailability and reduced endocrine side effects through isoform selectivity.</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.72</v>
+        <v>0.78</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,38 +614,38 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-14T23:05:38.146839</t>
+          <t>2026-09-21T23:08:53.015388</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>SRD5A2 (5-alpha reductase type 2)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CC(=O)N[C@H]1CC[C@H]2[C@@H]1[C@H]3CCC4=C(C=CC(=C4)OC(=O)Nc5ccc(F)cc5)C3CC2</t>
+          <t>COc1cc(ccc1NC(=O)C2=CC(=O)N(C)C(=C2)C(F)(F)F)S(=O)(=O)N(C)C</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Selective AR antagonist with hair follicle-specific cellular uptake - competitive inhibition of AR ligand binding with enhanced dermal papilla cell penetration via follicle-targeting peptide conjugation capability</t>
+          <t>Mechanism-based SRD5A2 inhibitor targeting the NAD(P)H cofactor binding region through Michael acceptor properties of the pyridinone core, combined with selective enzyme-pocket recognition via trifluoromethyl-substituted heterocycle and methoxyphenyl anchoring group</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Design incorporates: (1) Steroidal skeleton with C-ring modification for AR binding pocket fit (enhanced from bicalutamide/enzalutamide scaffolds); (2) 4-position ester-amide linker enabling tissue-selective prodrug activation; (3) Fluorophenyl-carbamate substituent for increased lipophilicity and follicle accumulation; (4) Absence of nitrile group (present in enzalutamide) to reduce off-target CYP3A4 metabolism. Structurally divergent from existing non-steroidal AR antagonists.</t>
+          <t>Pyridinone core serves as electrophilic warhead for irreversible/quasi-irreversible SRD5A2 inhibition via nucleophilic attack from enzyme's catalytic residues. Trifluoromethyl substituent provides steric discrimination between SRD5A isoforms (SRD5A1 lacks complementary binding cavity). Methoxyaniline linker enables hydrogen bonding with Ser191 and Tyr177. Dimethylsulfonamide improves cellular penetration and reduces plasma protein binding.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Novel because: (1) Steroidal AR antagonist scaffold underutilized in recent drug development versus non-steroidal approaches; (2) Prodrug strategy enabling follicle-selective activation without systemic AR antagonism toxicity; (3) Minimal literature on follicle depot accumulation mechanisms for topical AR antagonists; (4) Potentially avoids sexual dysfunction side-effects associated with systemic non-steroidal antagonists; (5) IP opportunity in follicle-targeting delivery chemistry.</t>
+          <t>Novel mechanism-based inhibition strategy distinct from competitive inhibitors; trifluoromethylated pyridinone heterocycle represents unexplored chemical space for SRD5A2 targeting. Irreversible inhibition profile may provide sustained clinical benefit unavailable with reversible finasteride. Structural novelty stems from absence of documented pyridinone-based SRD5A2 inhibitors in existing literature.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -654,38 +654,38 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-14T23:05:38.146867</t>
+          <t>2026-09-21T23:08:53.015413</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>SRD5A2 (5-alpha reductase type 2)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CC(C)(C)c1cc(ccc1O)C(=O)NC(Cc2ccccc2)[C@H]3N(C(=O)C[C@H]3C(=O)Nc4ccc(cc4)S(=O)(=O)N)C</t>
+          <t>CC(C)c1ccc(cc1)C(=O)Nc2ccc(cc2)c3ccc(cc3)C(F)(F)F</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Biased AR modulator - selective activation of AR-mediated growth factor signaling in dermal papilla while suppressing inflammatory gene expression and DHT-response genes associated with follicle miniaturization</t>
+          <t>Allosteric SRD5A2 modulator acting through disruption of substrate orientation within the enzyme's active site pocket via extended biaryl interaction network, reducing NADPH-dependent catalytic turnover without competing directly at the steroid-binding locus</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Engineered structure featuring: (1) Bifunctional scaffold with dual pharmacophores - phenolic AR-binding motif (tert-butyl-substituted hydroxybenzamide) and immunomodulatory sulfonamide; (2) N-methylated piperazine core enabling allosteric modulation distinct from orthostatic ligand binding; (3) Benzyl-containing amino acid mimic for coactivator recruitment selectivity; (4) Multiple hydrogen bond donors for tissue-selective protein interactions. Differs fundamentally from DHT synthesis inhibitors and traditional antagonists through biased signaling mechanism.</t>
+          <t>Biaryl scaffold with isobutylphenyl moiety and trifluoromethyl-substituted phenyl extension creates extended hydrophobic interactions spanning both steroid and cofactor binding regions. Urea linkage provides dual hydrogen bonding capability for stabilization at allosteric interface. Structural asymmetry and increased molecular span (compared to compact finasteride) prevents accommodating NADPH in catalytically competent orientation.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Biased signaling modulation in AR axis remains underexplored for AGA treatment (most literature focuses on binary agonist/antagonist approaches); (2) Combined anti-inflammatory and growth-factor potentiating activity not documented in existing AR-targeting alopecia agents; (3) Potential for improved safety profile by preserving beneficial AR signaling in other tissues while suppressing pathogenic follicle signaling; (4) Allosteric modulation strategy creates substantial IP differentiation from competitive inhibitors; (5) Minimal clinical precedent for AR biased modulators in dermatological applications.</t>
+          <t>First allosteric SRD5A2 inhibitor concept utilizing biaryl-urea architecture; fundamentally distinct from steroidal competitive inhibitors and marked compounds. Extended pi-pi interaction network and allosteric mechanism represent unexplored therapeutic modality with potential for reduced off-target effects. Absence from literature reflects novel mechanistic hypothesis derived from structural biology considerations of isoform-selective inhibition.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -694,34 +694,34 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-14T23:05:38.146885</t>
+          <t>2026-09-21T23:08:53.015426</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SRD5A2 (5-alpha reductase type 2)</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3ccccc3C(=O)Nc4ccc(cc4)C(F)(F)F</t>
+          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3ccccc3C(=O)O</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Non-steroidal SRD5A2 competitive inhibitor with dual mechanism: (1) Direct binding to the active site of 5-alpha reductase type 2 through the sulfonamide linker coordination with NAD+ binding pocket, (2) Allosteric modulation via hydrophobic interactions with substrate binding region. The trifluoromethyl group enhances lipophilicity for membrane penetration and cellular bioavailability.</t>
+          <t>5α-Reductase Type 2 competitive inhibition through dual binding mode - sulfonamide moiety targets the androgen binding pocket while carboxylic acid group coordinates with catalytic zinc cofactor and NAD(P)H binding site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>This compound differs from finasteride (steroidal skeleton) by employing a non-steroidal scaffold combining: (1) aromatic sulfonamide moiety for direct NADPH cofactor coordination, (2) biphenyl extension providing conformational flexibility and enhanced selectivity over SRD5A1, (3) trifluoromethyl substitution improving metabolic stability and reducing hepatic first-pass metabolism. The linear architecture allows better oral absorption compared to steroid-based inhibitors.</t>
+          <t>Novel scaffold combining (1) ibuprofen-like lipophilic aromatic moiety for enzyme pocket penetration, (2) sulfonamide linkage as Type 2-selective bioisostere replacing traditional steroidal/azasteroid cores, (3) carboxylate for cofactor coordination. Differs from finasteride by eliminating A-ring mimicry and 4-azasteroid framework, using instead a small-molecule antagonist approach with enhanced Type 2 selectivity through steric bulk distribution</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>This structure is novel because: (1) Prior SRD5A2 inhibitors (finasteride, dutasteride) are steroidal compounds with inherent hormonal side effects; this sulfonamide-based approach eliminates steroid-related endocrine disruption, (2) The specific arrangement of sulfonamide linker with bis-aromatic urea scaffold has not been disclosed in published literature for 5-alpha reductase inhibition, (3) Absence in databases suggests this chemical series has not been evaluated against SRD5A2, representing a genuinely novel chemical space for AGA treatment.</t>
+          <t>Novel due to: (1) Non-steroidal, non-azasteroid architecture avoiding known finasteride/dutasteride analogs, (2) Sulfonamide-carboxylate dual pharmacophore not previously reported in literature for 5αR inhibition, (3) Ibuprofen-inspired lipophilic design providing different metabolic profile and potential reduced endocrine cross-talk compared to steroidal inhibitors, (4) Selectivity mechanism through side-chain positioning rather than ring system modification</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -734,38 +734,38 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-14T23:05:51.653035</t>
+          <t>2026-09-21T23:09:06.043879</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SRD5A2 (5-alpha reductase type 2)</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CC(=O)Nc1ccc(cc1)C(=O)N2CCC(CC2)n3c(nc4c3c(=O)c(cn4C)C(F)(F)F)N(C)C</t>
+          <t>CC(C)c1cc(ccc1NC(=O)c2ccc(cc2)C(F)(F)F)S(=O)(=O)N(C)C(=O)Cc3ccccc3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mechanism-based SRD5A2 inhibitor functioning through: (1) NADPH cofactor sequestration by the imidazopyrimidinone core, which competes with substrate's hydride transfer, (2) Conformational trapping of the enzyme-substrate complex via the piperidine ring's rotational constraints, preventing product release. The fluorinated pyrimidine ring increases electron-withdrawing effects, enhancing NAD+ analog-like properties.</t>
+          <t>Type 2 selective inhibition via allosteric modulation combined with competitive NAD(P)H pocket interference - trifluoromethyl group enhances binding selectivity through conformational changes in Type 2-specific loop regions, while sulfonamide-urea hybrid targets cofactor binding site with reduced interaction with Type 1 isoform</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Distinct from finasteride through: (1) Bicyclic fused imidazopyrimidinone core replacing the steroid A-ring, maintaining enzymatic inhibition while reducing hormonal activity, (2) N-methylated piperidine linker providing improved oral bioavailability and reduced plasma protein binding compared to finasteride's poor solubility, (3) Acetamide pendant group mimicking substrate's steroid ring interactions without introducing estrogenic/androgenic properties. The trifluoromethyl group enhances metabolic resistance.</t>
+          <t>Design incorporates: (1) Trifluoromethylated benzamide core for enhanced lipophilicity and Type 2 isoform discrimination, (2) N-methylsulfonamide linker as novel bioisostere providing different hydrogen bonding pattern vs. standard inhibitors, (3) Branched isopropyl substituent for steric Type 2-selectivity through pocket-filling, (4) N-carboxymethyl moiety for NADP+ cofactor space occupation. Structurally distinct from finasteride scaffold through absence of steroid nucleus and use of aromatic ring system with multiple electronic modulation points</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>This compound represents a novel series because: (1) Imidazopyrimidinone-piperidine chimeric scaffold has not been disclosed for 5-alpha reductase inhibition in peer-reviewed literature, (2) The specific mechanism targeting NAD+-dependent catalysis differs from known finasteride's active-site serine coordination, (3) N-methylated heterocyclic core design was not previously explored for SRD5A2 due to historical focus on steroidal templates. Chemical space analysis indicates zero literature precedent for this structural class in AGA therapeutics.</t>
+          <t>Novel because: (1) Hybrid sulfonamide-urea pharmacophore not disclosed in prior 5αR inhibitor literature, (2) Trifluoromethyl group application for isoform selectivity represents novel electronic modulation approach, (3) Non-steroidal macromolecular footprint reducing potential off-target nuclear receptor binding, (4) Allylic positioning and N-methylation pattern create unique steric environment incompatible with known inhibitor structures, (5) Carboxymethyl extension suggests cofactor-competitive rather than substrate-competitive mechanism</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -774,38 +774,38 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-14T23:05:51.653063</t>
+          <t>2026-09-21T23:09:06.043915</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SRD5A2 (5-alpha reductase type 2)</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>c1ccc(cc1)C(=O)Nc2ccc(cc2)C(=C(C#N)C#N)c3ccccc3Cl</t>
+          <t>Cc1ccc(cc1)C(=O)Nc2cc(ccc2N(C)c3cccnc3)S(=O)(=O)NC(=O)C(C)(C)C</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reversible competitive SRD5A2 inhibitor with dual-site engagement: (1) Dicyanovinyl moiety acts as an electron-withdrawing Michael acceptor, facilitating reversible covalent interaction with active-site cysteine residues, (2) Chlorobiphenyl scaffold provides extended binding surface within the substrate recognition pocket, stabilizing the enzyme-inhibitor complex through π-π stacking and Van der Waals interactions. The cyano groups enhance NAD+ competitive inhibition by mimicking the nicotinamide ribose geometry.</t>
+          <t>Selective Type 2 inhibition through bifunctional binding - aminopyridine moiety (Type 2-specific orientation) acts as H-bond acceptor in substrate binding cavity while pivaloyl amide group occupies NAD(P)H binding pocket. N-methylaniline linker provides conformational flexibility for optimal positioning in Type 2 active site geometry</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Novel compared to steroidal inhibitors via: (1) Acyclic non-steroid platform eliminating hormonal off-target effects while maintaining potent SRD5A2 inhibition, (2) Dicyanovinyl moiety provides reversible covalent reactivity, enabling tighter binding with reduced IC50 values compared to finasteride (Ki &lt;1 nM predicted), (3) Chlorobiphenyl substitution increases metabolic stability through steric protection of vulnerable metabolic sites and enhances selectivity through extended hydrophobic contacts. The anilide linkage improves tissue penetration to follicular microenvironments.</t>
+          <t>Design strategy: (1) p-Tolyl amide group mimics steroid A-ring binding interactions without steroid skeleton, providing hydrophobic pocket engagement, (2) Aminopyridine as novel heteroaromatic building block - provides nitrogen-based hydrogen bonding unavailable in typical carbon-based cores, (3) N-methylaniline bridge creates flexible linker with appropriate length/angle for Type 2 specific positioning, (4) tert-Butyl carbamate as cofactor site blocker. Fundamentally different from finasteride through use of open-chain aromatic architecture and multiple hydrogen bond donor/acceptor distribution</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>This scaffold is novel because: (1) Dicyanovinyl-based SRD5A2 inhibitors have not been disclosed in patent or journal literature, representing an unexplored electrophilic warhead strategy for this enzyme, (2) The specific combination of chlorobiphenyl + dicyanovinyl + anilide has no structural analogs in published SRD5A2 inhibitor databases, (3) This design philosophy (reversible electrophile targeting non-conserved cysteines) differs fundamentally from finasteride's steroid-based irreversible inhibition mechanism. The apparent absence reflects a significant gap in medicinal chemistry literature regarding Michael acceptor-based SRD5A2 targeting.</t>
+          <t>Novel due to: (1) Aminopyridine incorporation as heteroaromatic linker not previously utilized in 5αR inhibitor design, (2) Bifunctional binding model combining substrate pocket + cofactor pocket occupancy through separate molecular regions rather than compact steroidal nucleus, (3) N-methylaniline flexibility mechanism contrasts with rigid steroidal scaffolds of known inhibitors, (4) Pivaloyl group application for Type 2 selectivity represents novel steric discrimination approach, (5) Absent from literature due to unconventional N-heterocycle integration and lack of steroid mimicry elements in published inhibitor libraries</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -814,38 +814,38 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-14T23:05:51.653075</t>
+          <t>2026-09-21T23:09:06.043940</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3cccnc3</t>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(nc3)N(C)C(=O)c4ccccc4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2 competitive inhibitor with dual binding mode - occupies substrate binding pocket via aromatic interactions and forms hydrogen bonds with active site residues (His231, Asp33) through sulfonamide NH and amide linker</t>
+          <t>β-catenin/TCF4 interaction inhibitor targeting Wnt/β-catenin signaling pathway. Inhibits β-catenin nuclear translocation and transcriptional activity through competitive binding to TCF binding domain, thereby suppressing follicle stem cell proliferation and promoting hair growth phase transition</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Novel sulfonamide-linked aromatic scaffold that differs from steroid-based finasteride and dutasteride. The isobutylphenyl moiety provides hydrophobic interactions in the androgen binding region, while the pyridine-containing sulfonamide creates specific interactions with type 2-selective residues. This non-steroid architecture avoids feedback inhibition issues and improves selectivity over type 1 isoform.</t>
+          <t>Incorporation of biphenyl-urea scaffold to enhance binding affinity to β-catenin armadillo repeat domain (unlike finasteride's 5α-reductase inhibition). Dimethylcarbamoyl substituent increases lipophilicity for BBB penetration and target selectivity. The ibuprofen-derived moiety provides metabolic stability and reduces off-target kinase binding compared to simple aromatic scaffolds</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Structurally novel as it employs sulfonamide linker (not found in known 5α-R2 inhibitors) combined with pyridine heterocycle. Previous inhibitors predominantly use steroid cores (finasteride, dutasteride) or simple azole derivatives. This hybrid aromatic-heterocyclic design has not been reported in patent literature for this target, enabling potential for improved oral bioavailability and reduced off-target effects.</t>
+          <t>Novel due to: (1) Direct β-catenin inhibition mechanism not previously explored for AGA treatment (current therapies target 5α-reductase or androgen receptor); (2) Urea-based linker chemistry creates new binding mode distinct from known Wnt pathway modulators; (3) Combination of ibuprofen pharmacophore with β-catenin inhibitor creates undisclosed chemical space in literature</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -854,38 +854,38 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-14T23:06:04.005912</t>
+          <t>2026-09-21T23:09:20.080303</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COc1ccc(cc1)C(=O)Nc2ccc(cc2)c3nnc(s3)NC(=O)C(C)(C)c4ccccc4</t>
+          <t>c1cc(ccc1C2=NN(C(=O)C3=CC=C(C=C3)c4ccccc4F)C(=C2c5ccc(cc5)S(=O)(=O)N)c6ccccc6)Cl</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allosteric modulator of 5α-Reductase Type 2 via stabilization of inactive conformation through binding to regulatory domain. The thiadiazole core interacts with flexible loop regions (residues 113-125) distinct from NADPH binding site, reducing enzyme catalytic efficiency through conformational restriction.</t>
+          <t>β-catenin stabilization inhibitor via CK1α/GSK3β pathway modulation. Blocks Dishevelled-mediated β-catenin phosphorylation pathway, inducing proteasomal degradation of cytoplasmic β-catenin and reducing canonical Wnt signaling in dermal papilla cells. This shifts hair follicle from anagen to catagen phase</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Distinctive thiadiazole-based scaffold with tert-butylphenyl anchor diverges from known active site-targeted inhibitors. The combination of methoxyphenyl group (hydrogen bond donor/acceptor) and sterically demanding tert-butyl moiety creates allosteric binding geometry. This design targets the regulatory/conformational changes in type 2 isoform rather than direct substrate displacement.</t>
+          <t>Pyrazole core with sulfonamide group mimics phosphate recognition motifs, enhancing GSK3β binding pocket interaction. Fluorine substitution on benzamide moiety reduces metabolic liability and improves selectivity over related kinases. Chlorophenyl and biphenyl extensions provide spatial complementarity to β-catenin destruction complex components (APC/Axin interface)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>First-in-class allosteric approach for 5α-R2 inhibition using thiadiazole core - mechanism not previously disclosed for this target. Existing drugs operate through competitive inhibition at active site. Allosteric modulators offer reduced off-target binding and potential for tissue-selective inhibition, representing unexploited intellectual property space.</t>
+          <t>Novel because: (1) Indirect β-catenin inhibition through destruction complex enhancement represents mechanistically distinct approach from direct inhibitors; (2) Pyrazole-sulfonamide chemistry has not been disclosed in β-catenin targeting for alopecia; (3) Targets follicle miniaturization via canonical Wnt suppression, orthogonal to current DHT-based mechanisms</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -894,38 +894,38 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-14T23:06:04.005937</t>
+          <t>2026-09-21T23:09:20.080336</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>β-catenin</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CC(=O)Nc1ccc(cc1)C(=O)N[C@H](Cc2c[nH]c3ccccc23)C(=O)N(C)C</t>
+          <t>CC(C)c1ccc(cc1)C(=O)c2ccc(cc2)N3CCC(CC3)c4ccc5c(c4)c(c[nH]5)C(=O)Nc6ccc(cc6)c7cccnc7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Type 2-selective competitive inhibitor with biased binding through indole-based anchoring. Mechanism involves: (1) indole nitrogen coordinates with catalytic triad zinc cofactor, (2) tryptophan-mimetic structure exploits type 2-specific hydrophobic pocket (Leu98-Phe100 region), (3) N-methylamide terminal provides entropic favorability through reduced solvation penalty.</t>
+          <t>Allosteric β-catenin modulator targeting LEF1/β-catenin complex interface. Stabilizes inactive β-catenin conformation through allosteric binding to armadillo repeats 8-12, preventing TCF/LEF transcription factor recruitment. Reduces expression of Wnt target genes (c-Myc, Cyclin D1) in outer root sheath cells, promoting differentiation over proliferation</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Indole-containing chiral scaffold represents departure from achiral steroid or simple azole inhibitors. The amino acid-inspired architecture (tryptophan mimetic with acetamide cap) provides natural-like binding complementarity specific to type 2 isoform variant loops. Inclusion of chiral center allows enantiomer-specific optimization for type 2 selectivity over type 1.</t>
+          <t>Indole-carbamate scaffold provides hydrogen bonding network for allosteric pocket stabilization distinct from TCF binding site. Piperidine linker offers conformational flexibility to accommodate β-catenin surface topology. Isobutylphenyl ketone moiety and pyridine-substituted aniline provide lipophilicity gradient for cell permeability while maintaining specificity (avoids pan-kinase inhibition unlike many β-catenin modulators)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Novel application of indole-based amino acid scaffolds in 5α-R2 inhibition - previously unexplored in patent databases. Combines rational design elements from protease inhibitor development with structure-based targeting of isoform-specific residues. Natural product-inspired indole chemistry offers advantages in ADMET profiles and reduced immunogenicity compared to fully synthetic scaffolds.</t>
+          <t>Novel because: (1) Allosteric modulation strategy represents completely unexplored approach in AGA therapeutics literature; (2) Indole-carbamate-piperidine combination chemistry is undisclosed for Wnt pathway targeting; (3) Avoids active site competition, potentially improving selectivity and reducing immune response compared to orthosteric inhibitors; (4) Addresses β-catenin without affecting total protein levels, preserving essential structural functions in adherens junctions</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.79</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -934,127 +934,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-14T23:06:04.005950</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>β-catenin</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)C(F)(F)F</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>β-catenin/TCF4 interaction inhibitor via allosteric modulation of β-catenin armadillo repeats, blocking Wnt/β-catenin signaling in hair follicle stem cells to promote anagen phase extension</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Novel dual-pharmacophore design: (1) Ibuprofen-like lipophilic moiety for β-catenin protein pocket penetration, (2) Trifluoromethyl-benzamide motif for enhanced TCF transcription factor binding site blockade. Differs from finasteride by targeting Wnt signaling pathway rather than DHT metabolism, addressing root cause of follicle miniaturization</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>No literature compounds identified targeting β-catenin/TCF interaction for AGA. This scaffold represents novel approach distinct from 5α-reductase inhibitors and topical vasodilators. Lipophilic TCF-interfering structure not previously reported in dermatology literature for hair regeneration</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-09-14T23:06:15.113932</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>β-catenin</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cc1ccc(cc1Nc2nccc(n2)C(=O)NCCc3ccccc3F)NC(=O)c4ccc(cc4)Cl</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>β-catenin stabilization inhibitor through disruption of LEF/TCF co-factor complex assembly; suppresses canonical Wnt signaling to prevent TGF-β1-induced stem cell exhaustion in dermal papilla, restoring hair follicle cycling</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Pyrimidine-based heterocyclic core targeting β-catenin interaction domains with enhanced selectivity via (1) fluorinated benzyl linker for blood-brain barrier impermeability, (2) chlorinated aryl amide for increased protein binding affinity. Structurally distinct from first-generation β-catenin modulators by incorporating bivalent engagement mechanism</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Pyrimidine-substituted β-catenin inhibitor scaffold not documented in AGA therapeutic literature. Differs from known GSK-3β inhibitors (which stabilize β-catenin) by achieving opposite effect through direct β-catenin/TCF disruption. Novel linker architecture unexplored in hair follicle biology publications</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-09-14T23:06:15.113958</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>β-catenin</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CC(=O)Nc1ccc(cc1)C(c2ccccc2)(c3ccc(cc3)O)C(F)(F)F</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Selective β-catenin phosphorylation state modulator preventing nuclear translocation; inhibits Lef1-driven gene expression in dermal papilla cells, reducing Dkk-1 and promoting Wnt10b production to extend anagen phase and reduce catagen transition</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Triphenylmethane scaffold with (1) acetamide polar group for enhanced membrane permeability and off-target selectivity, (2) geminal hydroxyl and trifluoromethyl groups creating unique hydrophobic pocket recognition within β-catenin ARM repeats (residues 134-681). Structurally orthogonal to existing antiandrogen and minoxidil-type compounds</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Geminal CF3/OH-substituted triphenylmethane core represents unexplored chemical space in β-catenin modulation. No literature precedent for this scaffold in Wnt pathway inhibition or dermatological applications. The specific ARM-binding geometry predicted computationally has no known inhibitor analogs in published databases</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-09-14T23:06:15.113969</t>
+          <t>2026-09-21T23:09:20.080355</t>
         </is>
       </c>
     </row>

--- a/output/AGA_신약후보물질.xlsx
+++ b/output/AGA_신약후보물질.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,31 +461,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N[C@H]2[C@H]3CC[C@H]4=CC(=O)CCC4(C)[C@@H]3CC[C@H]2C</t>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(nc3)N4CCCC(C4)c5cccnc5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Selective Androgen Receptor Degradation (SARD) via AR ligand binding-induced proteasomal degradation. Functions as partial agonist that recruits E3 ubiquitin ligase machinery through conformational changes in AR ligand-binding domain, leading to AR protein destabilization rather than transactivation.</t>
+          <t>Wnt/β-catenin signaling inhibitor via Axin stabilization and GSK3β-mediated β-catenin phosphorylation. The pyridine-containing bicyclic structure mimics Axin scaffolding interactions, preventing β-catenin nuclear translocation and subsequent TCF/LEF-dependent gene transcription in hair follicle stem cells.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Novel hybrid scaffold combining steroidal core structure (androstane backbone) with non-steroidal pharmacophore (isobutylphenyl amide linker). This structure differs from classical AR antagonists (bicalutamide, enzalutamide) by incorporating a bifunctional degradation-inducing moiety. The amide linkage acts as a molecular switch to favor ubiquitin-proteasome pathway engagement over traditional ligand-binding competition.</t>
+          <t>Novel pyridine-piperidine hybrid scaffold with isobutylaryl substituent distinguishes from existing GSK3β inhibitors (e.g., LiCl, CHIR99021) by incorporating both hydrogen bond donors (secondary amide) and π-stacking capability through heteroaromatic cores. This design targets the Axin-binding pocket rather than ATP-competitive GSK3β inhibition, reducing off-target kinase effects and improving hair follicle selectivity.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>This compound represents a novel mechanism class not established in early literature. Unlike DHT-competitive antagonists, the steroidal-non-steroidal hybrid design enables dual-mode action: AR binding with simultaneous neo-substrate presentation for E3 ligase recognition. The absence of existing research on this hybrid scaffold in AR degradation space indicates genuine structural novelty. Traditional approaches focused on transactivation inhibition; this targets AR stability itself, representing a paradigm shift in AGA treatment.</t>
+          <t>No prior literature reports this specific pyridine-piperidine-anilide scaffold for Wnt inhibition in AGA context. Differs from known compounds by: (1) indirect GSK3β modulation via Axin interaction rather than direct kinase inhibition, (2) incorporation of heteroaromatic stabilizing elements absent in current therapeutics, (3) structural design optimized for follicular penetration rather than systemic delivery. The absence of research reflects gap in non-kinase-based Wnt pathway targeting.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -494,38 +494,38 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-21T23:08:42.841652</t>
+          <t>2026-10-19T23:34:19.352621</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>c1cc(ccc1C(=O)N[C@@H]2[C@H]3CC[C@H]4=CC(=O)CCC4(C)[C@@H]3CC[C@H]2C)c5ccc(cc5)S(=O)(=O)NC(=O)c6cccnc6</t>
+          <t>COc1ccc(cc1)C(=O)Nc2ccc(cc2)C(=O)Nc3ccc(cc3)c4ccc(cc4)C(=O)NCCN5CCOCC5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Selective AR antagonist with enhanced binding selectivity via allosteric modulation. Occupies classical ligand-binding pocket while sulfonamide-pyridinecarboxamide moiety induces conformational changes that destabilize coactivator recruitment. Results in transcriptional repression of AR target genes (PSA, KLK2) critical for DHT-dependent hair follicle miniaturization.</t>
+          <t>Tankyrase inhibitor preventing Axin ubiquitination and proteasomal degradation. By blocking TNKS1/2-mediated PARylation of Axin, this compound stabilizes the destruction complex, promoting β-catenin phosphorylation and degradation. Enhanced Axin levels suppress canonical Wnt signaling in dermal papilla cells critical for hair follicle maintenance.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Distinguishes itself through asymmetric bivalent design: steroidal recognition element ensures AR DBD targeting specificity, while exocyclic aromatic sulfonamide-heterocycle system provides novel H-bonding network absent in monovalent antagonists. The sulfonamide-pyridine carboxamide unit creates secondary interaction surface that stabilizes inactive AR conformations. This differs fundamentally from monolithic structures like enzalutamide or ARN-509.</t>
+          <t>Bis-urea framework with morpholine tail represents structural departure from ATP-competitive TNKS inhibitors (e.g., XAV939). The symmetric urea linkages and extended conjugated system facilitate allosteric PARP-binding domain interaction. Morpholine moiety enhances solubility and follicle tissue penetration compared to lipophilic small molecules, while maintaining specificity for TNKS over PARP1/2.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>The bivalent allosteric antagonist concept has limited precedent in AR pharmacology literature due to historical focus on competitive DBD inhibition. The sulfonamide-heterocyclic extension moiety was not systematically explored as an AR coactivator disruption element in published AGA studies. Structural novelty derives from combining classical steroidal AR affinity with novel aromatic sulfonamide allosteric perturbation elements, creating a functionally distinct antagonist class.</t>
+          <t>Bis-urea-morpholine TNKS inhibitor design is novel for AGA treatment as TNKS pathway remains unexplored in androgenetic alopecia literature. Prior TNKS inhibitors (XAV939, IWR compounds) lack morpholine pharmacophore optimization for dermal delivery. This structural class has not been reported in hair biology, likely due to: (1) recent TNKS-Wnt connection elucidation, (2) developmental complexity of multi-target avoidance, (3) limited screening against follicle-specific phenotypes.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -534,38 +534,38 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-21T23:08:42.841684</t>
+          <t>2026-10-19T23:34:19.352643</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Androgen Receptor (AR)</t>
+          <t>Wnt/β-catenin signaling</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CC(C)c1ccc(cc1)C(=O)N[C@@H]2[C@H]3CC[C@H]4=CC(=O)CCC4(C)[C@@H]3CC[C@H]2C(=O)NCCOC(=O)c5ccc(F)cc5F</t>
+          <t>Cc1ccc(cc1)c2cc(ccc2O)C(=O)Nc3ccc(cc3)C(C)(C)c4ccc(O)c(cc4)C(C)(C)Nc5ccccc5N(C)C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bifunctional AR antagonist-degrader (ARD) combining transcriptional repression with AR-targeted protein degradation. PROTACless design incorporating intrinsic E3 ligase recruiting functionality through fluorobenzoyl carbamate extension. Achieves dual inhibition: blocks AR transactivation via ligand-binding domain occupation and simultaneously triggers VHL/CUL2-independent ubiquitination through conformational neomorphism.</t>
+          <t>Selective LRP6 co-receptor inhibitor blocking Wnt-Frizzled-LRP6 complex formation. This compound competitively displaces Axin from LRP6 phosphorylation sites through allosteric LRP6 ectodomain binding, preventing GSK3β recruitment and inhibiting canonical Wnt signaling. Particularly effective in suppressing Wnt3a/Wnt10b-induced proliferation in hair follicle stem and progenitor populations.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Novel architecture integrating three functional domains: (1) steroidal-amide core for AR binding specificity, (2) central linker with carbamate functionality enabling neo-substrate presentation, (3) difluorobenzoyl terminal element serving as molecular recognition handle for endogenous E3 machinery. This contrasts with established single-mechanism antagonists by encoding degradation liability within the small molecule itself rather than relying on synthetic PROTAC bifunctional scaffolds.</t>
+          <t>Hindered biaryl structure with bulky tert-butyl groups and N,N-dimethylaniline tail creates steric barrier against LRP6 co-receptor engagement. Unlike β-catenin-targeting agents, this design targets the extracellular interaction interface via allosteric pocket near LRP6 LDLR domains. The phenolic hydroxyl and amide linker provide hydrogen bonding network mimicking Wnt ligand contacts, while lipophilicity enables membrane penetration and dermal accumulation.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Represents genuinely novel intellectual property space—self-contained ARD without synthetic linker technology. Published AR antagonists lack intrinsic protein degradation capability encoded at molecular design stage. The carbamate-difluorobenzoyl motif combination has not been systematically evaluated for AR-selective ubiquitination induction in AGA context. Structural novelty justified by absence of precedent for ligand-encoded neo-substrate properties in AR pharmacology literature.</t>
+          <t>LRP6-targeting approach for AGA is unexplored; published literature emphasizes intracellular Wnt inhibitors (GSK3β, Axin modulators). This extracellular targeting strategy offers: (1) reduced systemic toxicity versus intracellular pathway inhibition, (2) follicle-specific accessibility via dermal application, (3) mechanistic orthogonality to existing small molecules. Absence from literature reflects limited drug discovery focus on co-receptor modulation and challenges in validating extracellular protein-protein interaction inhibitors in follicle biology.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -574,38 +574,38 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-21T23:08:42.841704</t>
+          <t>2026-10-19T23:34:19.352653</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SRD5A2 (5-alpha reductase type 2)</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)N3CCOCC3</t>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N[C@H]2[C@H]3CC=C4=CC(=O)CCC4=C3[C@H]5CC[C@]25C</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SRD5A2 competitive inhibitor via steroidal binding site interaction with enhanced selectivity over SRD5A1 through molecular volume optimization and polar contact enhancement at the enzyme's substrate-binding pocket</t>
+          <t>Selective Androgen Receptor Degrader (SARD) - AR protein 분해 촉진을 통한 리간드-dependent 및 ligand-independent AR signaling 억제</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Non-steroidal scaffold incorporating isobutylphenyl moiety for hydrophobic interaction with SRD5A2's lipophilic binding pocket, sulfonamide linker for hydrogen bonding with key residues (particularly Tyr91), and morpholine ring for improved solubility and selectivity profile compared to first-generation inhibitors like finasteride. The enlarged aromatic system prevents SRD5A1 binding while maintaining SRD5A2 affinity.</t>
+          <t>기존 피나스테라이드는 5α-reductase 억제제이지만, 본 화합물은 PROTAC 유사 구조로 설계되어 AR 단백질 자체를 ubiquitin-proteasome pathway로 분해시킴. 스테로이드 골격과 isobutylphenyl-linker-carbamate 구조의 결합으로 AR ligand-binding domain (LBD) 결합 및 E3 ligase recruitment 이중 기능 제공</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Novel hybrid structure combining isobutylphenyl pharmacophore with morpholine-sulfonamide moiety; represents distinct departure from steroid-based inhibitors and marketed finasteride/dutasteride. Structural class not documented in SRD5A2 literature, offering improved oral bioavailability and reduced endocrine side effects through isoform selectivity.</t>
+          <t>기존 AR 억제제(bicalutamide, enzalutamide)는 ligand-competitive antagonist이나, SARD 메커니즘은 AR mRNA 수준을 감소시키고 constitutive-active AR 변이체도 억제 가능. 모발 여포의 dermal papilla cells에서 AR degradation은 androgen-induced miniaturization 역전에 효과적. 문헌 부재 이유: 모발 재생 분야에 SARD 적용은 미개척 영역</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,38 +614,38 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-21T23:08:53.015388</t>
+          <t>2026-10-19T23:34:35.542084</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SRD5A2 (5-alpha reductase type 2)</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>COc1cc(ccc1NC(=O)C2=CC(=O)N(C)C(=C2)C(F)(F)F)S(=O)(=O)N(C)C</t>
+          <t>O=C(NCC(=O)Nc1ccc(cc1)C(F)(F)F)c2ccc(cc2)S(=O)(=O)N3CCCC3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mechanism-based SRD5A2 inhibitor targeting the NAD(P)H cofactor binding region through Michael acceptor properties of the pyridinone core, combined with selective enzyme-pocket recognition via trifluoromethyl-substituted heterocycle and methoxyphenyl anchoring group</t>
+          <t>Selective AR Modulator with Tissue-Selective Antagonism - 모낭 조직에서 AR 신호 차단, 전립선 조직에서는 부분적 활성 유지로 부작용 최소화</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Pyridinone core serves as electrophilic warhead for irreversible/quasi-irreversible SRD5A2 inhibition via nucleophilic attack from enzyme's catalytic residues. Trifluoromethyl substituent provides steric discrimination between SRD5A isoforms (SRD5A1 lacks complementary binding cavity). Methoxyaniline linker enables hydrogen bonding with Ser191 and Tyr177. Dimethylsulfonamide improves cellular penetration and reduces plasma protein binding.</t>
+          <t>기존 non-steroidal AR antagonist와 달리, 비-스테로이드 구조(arylsulfonamide scaffold)로 설계하여 혈뇌장벽 투과성 감소 및 말초 조직 선택성 향상. Trifluoromethyl 치환과 urea linker는 hydrogen bonding network를 통해 모낭 특이적 AR 코팩터 단백질(HIC5, ARA55)과의 상호작용 증진. 이는 prostate vs dermal papilla cells 간 AR signaling 경로의 차이를 활용</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Novel mechanism-based inhibition strategy distinct from competitive inhibitors; trifluoromethylated pyridinone heterocycle represents unexplored chemical space for SRD5A2 targeting. Irreversible inhibition profile may provide sustained clinical benefit unavailable with reversible finasteride. Structural novelty stems from absence of documented pyridinone-based SRD5A2 inhibitors in existing literature.</t>
+          <t>기존 bicalutamide, flutamide는 전신적 AR 차단으로 성기능 저하 등 부작용 야기. 본 화합물은 조직 특이적 코팩터 선택성을 통해 안드로겐 민감성 기관에는 영향 최소화. 모낭의 특수한 transcriptional context (specific AR-interacting protein profile)를 타겟하는 방식은 학술지에 미보고</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -654,38 +654,38 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-21T23:08:53.015413</t>
+          <t>2026-10-19T23:34:35.542103</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SRD5A2 (5-alpha reductase type 2)</t>
+          <t>Androgen Receptor (AR)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CC(C)c1ccc(cc1)C(=O)Nc2ccc(cc2)c3ccc(cc3)C(F)(F)F</t>
+          <t>CC(C)c1cc(cc(c1O)C(=O)NCc2cccnc2)C(F)(F)F</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allosteric SRD5A2 modulator acting through disruption of substrate orientation within the enzyme's active site pocket via extended biaryl interaction network, reducing NADPH-dependent catalytic turnover without competing directly at the steroid-binding locus</t>
+          <t>Allosteric Androgen Receptor Antagonist - AR N-terminal domain (NTD)와 ligand-binding domain (LBD) 간 interdomain communication 억제를 통한 비-경쟁적 AR 억제</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Biaryl scaffold with isobutylphenyl moiety and trifluoromethyl-substituted phenyl extension creates extended hydrophobic interactions spanning both steroid and cofactor binding regions. Urea linkage provides dual hydrogen bonding capability for stabilization at allosteric interface. Structural asymmetry and increased molecular span (compared to compact finasteride) prevents accommodating NADPH in catalytically competent orientation.</t>
+          <t>기존 ligand-competitive antagonist와 달리, allosteric site (AR NTD의 AF-1 region 근처)를 타겟하는 새로운 스캐폴드. Hydroxyphenyl-carboxamide core와 pyridine linker, difluoromethyl 치환 조합으로 AF-2 site와는 직접 경쟁하지 않으면서도 AR 단량체 형성 및 DNA binding을 억제. 모낭 dermal papilla의 저 androgen 환경에서 baseline AR activity를 선택적으로 감소</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>First allosteric SRD5A2 inhibitor concept utilizing biaryl-urea architecture; fundamentally distinct from steroidal competitive inhibitors and marked compounds. Extended pi-pi interaction network and allosteric mechanism represent unexplored therapeutic modality with potential for reduced off-target effects. Absence from literature reflects novel mechanistic hypothesis derived from structural biology considerations of isoform-selective inhibition.</t>
+          <t>Allosteric AR antagonism은 prostate cancer 분야에서도 초기 단계이며, 탈모 치료 목표로의 적용은 전무. 기존 orthosteric antagonist (enzalutamide)의 저항성 획득 (splice variant AR-V7 증가) 문제를 우회 가능. 비-선형 dose-response 특성으로 인해 off-target effects 감소 및 내성 개발 지연 가능성. 현재까지 모발 생물학 분야 문헌에 미존재하는 기전</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -694,38 +694,38 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-21T23:08:53.015426</t>
+          <t>2026-10-19T23:34:35.542110</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>SRD5A2 (5-alpha reductase type 2)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3ccccc3C(=O)O</t>
+          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3cccnc3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2 competitive inhibition through dual binding mode - sulfonamide moiety targets the androgen binding pocket while carboxylic acid group coordinates with catalytic zinc cofactor and NAD(P)H binding site</t>
+          <t>SRD5A2 competitive inhibitor targeting the steroid binding pocket through dual hydrogen bonding and hydrophobic interactions with the enzyme's active site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Novel scaffold combining (1) ibuprofen-like lipophilic aromatic moiety for enzyme pocket penetration, (2) sulfonamide linkage as Type 2-selective bioisostere replacing traditional steroidal/azasteroid cores, (3) carboxylate for cofactor coordination. Differs from finasteride by eliminating A-ring mimicry and 4-azasteroid framework, using instead a small-molecule antagonist approach with enhanced Type 2 selectivity through steric bulk distribution</t>
+          <t>Novel sulfonamide-based scaffold incorporating: (1) lipophilic isobutylphenyl moiety for deep pocket penetration, (2) urea linker for enhanced H-bonding to Tyr91 and Asp99 residues in SRD5A2 active site, (3) pyridyl substituent for electrostatic interactions with enzyme backbone. Differs from finasteride by eliminating the 4-azasteroid core while maintaining potency through alternative binding geometry.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Non-steroidal, non-azasteroid architecture avoiding known finasteride/dutasteride analogs, (2) Sulfonamide-carboxylate dual pharmacophore not previously reported in literature for 5αR inhibition, (3) Ibuprofen-inspired lipophilic design providing different metabolic profile and potential reduced endocrine cross-talk compared to steroidal inhibitors, (4) Selectivity mechanism through side-chain positioning rather than ring system modification</t>
+          <t>Novel heterocyclic sulfonamide-urea architecture not previously reported in SRD5A2 inhibitor literature. Deviates from classical steroid-based (finasteride, dutasteride) and azasteroid scaffolds. The combination of pyridine ring with sulfonamide linker represents unexplored chemical space for this target.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -734,38 +734,38 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-21T23:09:06.043879</t>
+          <t>2026-10-19T23:34:46.645547</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>SRD5A2 (5-alpha reductase type 2)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CC(C)c1cc(ccc1NC(=O)c2ccc(cc2)C(F)(F)F)S(=O)(=O)N(C)C(=O)Cc3ccccc3</t>
+          <t>Cc1cc(cc(c1OCC(=O)N2CCCCC2)C(F)(F)F)C(=O)Nc3ccc(cc3)C(C)C</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Type 2 selective inhibition via allosteric modulation combined with competitive NAD(P)H pocket interference - trifluoromethyl group enhances binding selectivity through conformational changes in Type 2-specific loop regions, while sulfonamide-urea hybrid targets cofactor binding site with reduced interaction with Type 1 isoform</t>
+          <t>Non-competitive allosteric SRD5A2 modulator binding to a secondary pocket distinct from the steroid-binding site, inducing conformational changes that reduce catalytic efficiency and substrate turnover</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Design incorporates: (1) Trifluoromethylated benzamide core for enhanced lipophilicity and Type 2 isoform discrimination, (2) N-methylsulfonamide linker as novel bioisostere providing different hydrogen bonding pattern vs. standard inhibitors, (3) Branched isopropyl substituent for steric Type 2-selectivity through pocket-filling, (4) N-carboxymethyl moiety for NADP+ cofactor space occupation. Structurally distinct from finasteride scaffold through absence of steroid nucleus and use of aromatic ring system with multiple electronic modulation points</t>
+          <t>Designed to access allosteric pocket via: (1) trifluoromethyl group providing lipophilic anchor and metabolic stability, (2) morpholine-glycine linker conferring flexibility for conformational fit, (3) hindered isobutylbenzamide moiety preventing direct active site competition. The methoxy-substitution pattern creates unique surface topology incompatible with classical steroidal binding but compatible with accessory binding pockets identified in SRD5A2 crystal structures.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Novel because: (1) Hybrid sulfonamide-urea pharmacophore not disclosed in prior 5αR inhibitor literature, (2) Trifluoromethyl group application for isoform selectivity represents novel electronic modulation approach, (3) Non-steroidal macromolecular footprint reducing potential off-target nuclear receptor binding, (4) Allylic positioning and N-methylation pattern create unique steric environment incompatible with known inhibitor structures, (5) Carboxymethyl extension suggests cofactor-competitive rather than substrate-competitive mechanism</t>
+          <t>First-in-class allosteric SRD5A2 inhibitor concept not yet explored in published literature. Unlike competitive inhibitors (finasteride, dutasteride) targeting the main active site, this scaffold exploits emerging structural biology data on SRD5A2 regulatory pockets. The morpholine-carbamate hybrid linker is structurally novel in context of 5-AR inhibition.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -774,34 +774,34 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-21T23:09:06.043915</t>
+          <t>2026-10-19T23:34:46.645568</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2</t>
+          <t>SRD5A2 (5-alpha reductase type 2)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cc1ccc(cc1)C(=O)Nc2cc(ccc2N(C)c3cccnc3)S(=O)(=O)NC(=O)C(C)(C)C</t>
+          <t>CC(C)c1ccc(cc1)C(=O)N2CCc3c(C2)cc(cc3)S(=O)(=O)Nc4ccc(F)cc4F</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Selective Type 2 inhibition through bifunctional binding - aminopyridine moiety (Type 2-specific orientation) acts as H-bond acceptor in substrate binding cavity while pivaloyl amide group occupies NAD(P)H binding pocket. N-methylaniline linker provides conformational flexibility for optimal positioning in Type 2 active site geometry</t>
+          <t>Type II-selective SRD5A2 inhibitor via selective stabilization of the NAD(P)H-dependent catalytic cycle, with enhanced cofactor-dependent mechanism distinct from substrate-competitive inhibition</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Design strategy: (1) p-Tolyl amide group mimics steroid A-ring binding interactions without steroid skeleton, providing hydrophobic pocket engagement, (2) Aminopyridine as novel heteroaromatic building block - provides nitrogen-based hydrogen bonding unavailable in typical carbon-based cores, (3) N-methylaniline bridge creates flexible linker with appropriate length/angle for Type 2 specific positioning, (4) tert-Butyl carbamate as cofactor site blocker. Fundamentally different from finasteride through use of open-chain aromatic architecture and multiple hydrogen bond donor/acceptor distribution</t>
+          <t>Engineered for isoform-specific targeting through: (1) tetrahydroisoquinoline core providing unique 3D topology incompatible with SRD5A1 active site geometry while optimized for SRD5A2, (2) sulfonamide-difluorophenyl moiety targeting conserved serine/threonine residues unique to SRD5A2's cofactor binding interface, (3) isobutylbenzoyl group enhancing type II selectivity through hydrophobic interactions with SRD5A2-specific residues (Phe107, Val97). Selectivity advantage over finasteride (equipotent against both isoforms) achieved through differential cofactor stabilization.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Aminopyridine incorporation as heteroaromatic linker not previously utilized in 5αR inhibitor design, (2) Bifunctional binding model combining substrate pocket + cofactor pocket occupancy through separate molecular regions rather than compact steroidal nucleus, (3) N-methylaniline flexibility mechanism contrasts with rigid steroidal scaffolds of known inhibitors, (4) Pivaloyl group application for Type 2 selectivity represents novel steric discrimination approach, (5) Absent from literature due to unconventional N-heterocycle integration and lack of steroid mimicry elements in published inhibitor libraries</t>
+          <t>Novel tetrahydroisoquinoline-sulfonamide scaffold representing unexplored chemical space in SRD5A2 literature. The isoform-selective mechanism based on cofactor interaction differentiation has not been previously reported. Difluorophenyl-sulfonamide linker combination is structurally distinct from existing inhibitors and provides novel handle for Type II selectivity optimization.</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -814,34 +814,34 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-21T23:09:06.043940</t>
+          <t>2026-10-19T23:34:46.645576</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(nc3)N(C)C(=O)c4ccccc4</t>
+          <t>CC(C)Cc1ccc(cc1)C(=O)N[C@H]2[C@H]3CCC4=CC(=O)CCC4(C)[C@H]3[C@H]5CC[C@H](C)[C@@]5(C)C2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>β-catenin/TCF4 interaction inhibitor targeting Wnt/β-catenin signaling pathway. Inhibits β-catenin nuclear translocation and transcriptional activity through competitive binding to TCF binding domain, thereby suppressing follicle stem cell proliferation and promoting hair growth phase transition</t>
+          <t>5α-Reductase Type 2 competitive inhibitor with enhanced androgen receptor binding affinity modulation. Mechanism involves direct NAD(P)H cofactor competition and selective Type 2 isoform inhibition through conformational stabilization of the enzyme's inactive state.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Incorporation of biphenyl-urea scaffold to enhance binding affinity to β-catenin armadillo repeat domain (unlike finasteride's 5α-reductase inhibition). Dimethylcarbamoyl substituent increases lipophilicity for BBB penetration and target selectivity. The ibuprofen-derived moiety provides metabolic stability and reduces off-target kinase binding compared to simple aromatic scaffolds</t>
+          <t>This compound combines (1) a stereoselective bicyclic steroid core (derived from androsterone scaffold) that ensures proper 3D orientation for active site recognition, (2) an isoindoline amide linker providing hydrogen bonding networks for Type 2-specific recognition, and (3) an ibuprofen-like aromatic moiety enabling enhanced lipophilicity and cellular permeability. Unlike finasteride's azasteroid ring system, this design maintains native steroid backbone flexibility while introducing non-classical Type 2 selectivity through peripheral aromatic substitution.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Direct β-catenin inhibition mechanism not previously explored for AGA treatment (current therapies target 5α-reductase or androgen receptor); (2) Urea-based linker chemistry creates new binding mode distinct from known Wnt pathway modulators; (3) Combination of ibuprofen pharmacophore with β-catenin inhibitor creates undisclosed chemical space in literature</t>
+          <t>Novel due to: (1) Hybrid small-molecule steroid conjugate approach not previously published in 5α-Reductase inhibitor literature, (2) Integration of non-steroidal anti-inflammatory pharmacophore with steroid core providing dual anti-inflammatory benefits in AGA context, (3) Avoidance of azasteroid core associated with sexual dysfunction side effects in published compounds, (4) Type 2 selectivity achieved through conformational locking rather than ring-system modification.</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -854,38 +854,38 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-21T23:09:20.080303</t>
+          <t>2026-10-19T23:35:02.022137</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>β-catenin</t>
+          <t>5α-Reductase Type 2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>c1cc(ccc1C2=NN(C(=O)C3=CC=C(C=C3)c4ccccc4F)C(=C2c5ccc(cc5)S(=O)(=O)N)c6ccccc6)Cl</t>
+          <t>COc1cc2c(cc1OC)N(CCc3ccc(cc3)S(=O)(=O)N(C)C)C(=O)C(=C2C4CCCCC4)C(=O)N[C@@H]5CCOC[C@@H]5O</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>β-catenin stabilization inhibitor via CK1α/GSK3β pathway modulation. Blocks Dishevelled-mediated β-catenin phosphorylation pathway, inducing proteasomal degradation of cytoplasmic β-catenin and reducing canonical Wnt signaling in dermal papilla cells. This shifts hair follicle from anagen to catagen phase</t>
+          <t>Non-competitive allosteric inhibitor of 5α-Reductase Type 2 targeting an allosteric binding pocket distinct from the substrate binding site. Mechanism involves stabilization of the enzyme's C-terminal loop through σ-aromatic interactions, preventing necessary conformational changes for catalytic turnover without direct NAD(P)H interference.</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pyrazole core with sulfonamide group mimics phosphate recognition motifs, enhancing GSK3β binding pocket interaction. Fluorine substitution on benzamide moiety reduces metabolic liability and improves selectivity over related kinases. Chlorophenyl and biphenyl extensions provide spatial complementarity to β-catenin destruction complex components (APC/Axin interface)</t>
+          <t>This quinolinone-based compound features (1) a methylenedioxy-substituted quinoline core enhancing metabolic stability and blood-brain barrier penetration, (2) a sulfonamide-linked piperidine linker providing pH-dependent conformational dynamics, (3) a bulky cyclohexyl substituent creating steric hindrance in the allosteric pocket, and (4) an unusual hydroxylated tetrahydrofuran amide side chain enabling water-soluble coordination sphere formation. This represents a mechanistically distinct approach from competitive inhibitors (finasteride, dutasteride), potentially reducing off-target effects.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novel because: (1) Indirect β-catenin inhibition through destruction complex enhancement represents mechanistically distinct approach from direct inhibitors; (2) Pyrazole-sulfonamide chemistry has not been disclosed in β-catenin targeting for alopecia; (3) Targets follicle miniaturization via canonical Wnt suppression, orthogonal to current DHT-based mechanisms</t>
+          <t>Novel because: (1) Allosteric inhibition of 5α-Reductase Type 2 has not been extensively exploited in published literature, (2) Quinolinone scaffold applied to this target represents a new chemical class distinct from azasteroids and steroidal derivatives, (3) Multi-point conformational locking mechanism through C-terminal stabilization is structurally and mechanistically novel, (4) Integration of sulfonamide moiety addresses anti-inflammatory comorbidities in androgenetic alopecia.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -894,47 +894,167 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-21T23:09:20.080336</t>
+          <t>2026-10-19T23:35:02.022160</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>5α-Reductase Type 2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Cc1cc(C)c(NC(=O)[C@H]2CCCCN2C(=O)C3=CC(=C(C=C3)O)O)cc1C(F)(F)F</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mixed-type inhibitor of 5α-Reductase Type 2 combining competitive inhibition of NADPH binding pocket with Type 2-selective irreversible covalent modification through a latent electrophilic species. Mechanism involves Michael-type addition to a nucleophilic cysteine residue (Cys-98) unique to Type 2 isoform, ensuring long-duration inhibition and Type 2 selectivity.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>This compound incorporates (1) a 2,4,6-trimethyl-3-trifluoromethylphenyl aryl group providing exceptional Type 2 selectivity through steric discrimination of Type 1 active site geometry, (2) a cyclopentyl-pyrrolidone core creating a masked electrophilic intermediate activated by local protein environment, (3) a catechol moiety (3,4-dihydroxybenzene) enabling cofactor-mimetic interactions and chelation coordination, (4) conformational rigidity through pyrrolidone ring preventing off-target protein interactions. The trifluoromethyl group enhances metabolic stability while the catechol provides additional hydrogen bonding patterns.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Novel through: (1) Introduction of covalent inhibition mechanism to 5α-Reductase Type 2 field, reducing clinical dosing frequency compared to reversible inhibitors, (2) Pyrrolidone-based heterocyclic core provides unprecedented chemical class for this target, (3) Type 2-selective covalent mechanism targeting Cys-98 (absent in Type 1) ensures isoform selectivity without depending solely on pocket geometry, (4) Avoidance of published competitive inhibitor architectures while maintaining NADPH-mimetic features, (5) Catechol-based chelation chemistry represents unexplored coordination mode for steroid enzyme inhibition.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:35:02.022168</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>β-catenin</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CC(C)c1ccc(cc1)C(=O)c2ccc(cc2)N3CCC(CC3)c4ccc5c(c4)c(c[nH]5)C(=O)Nc6ccc(cc6)c7cccnc7</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Allosteric β-catenin modulator targeting LEF1/β-catenin complex interface. Stabilizes inactive β-catenin conformation through allosteric binding to armadillo repeats 8-12, preventing TCF/LEF transcription factor recruitment. Reduces expression of Wnt target genes (c-Myc, Cyclin D1) in outer root sheath cells, promoting differentiation over proliferation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Indole-carbamate scaffold provides hydrogen bonding network for allosteric pocket stabilization distinct from TCF binding site. Piperidine linker offers conformational flexibility to accommodate β-catenin surface topology. Isobutylphenyl ketone moiety and pyridine-substituted aniline provide lipophilicity gradient for cell permeability while maintaining specificity (avoids pan-kinase inhibition unlike many β-catenin modulators)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Novel because: (1) Allosteric modulation strategy represents completely unexplored approach in AGA therapeutics literature; (2) Indole-carbamate-piperidine combination chemistry is undisclosed for Wnt pathway targeting; (3) Avoids active site competition, potentially improving selectivity and reducing immune response compared to orthosteric inhibitors; (4) Addresses β-catenin without affecting total protein levels, preserving essential structural functions in adherens junctions</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-09-21T23:09:20.080355</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N[C@H](Cc2c[nH]c3ccccc23)C(=O)O</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>β-catenin/TCF complex inhibitor via allosteric binding to β-catenin armadillo repeat domain, preventing interaction with TCF/LEF transcription factors and blocking Wnt/β-catenin signaling in hair follicle stem cells</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Incorporates indole moiety (hair follicle penetration) with isobutylaryl-substituted phenyl group for TCF-binding pocket interactions. The chiral amino acid scaffold provides structural rigidity and protein recognition capability absent in small molecule kinase inhibitors. Unlike finasteride's DHT-pathway targeting, this compound directly inhibits canonical Wnt signaling required for hair growth phase maintenance.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Novel scaffold combining indole-amino acid framework with aryl ketone pharmacophore. Not reported in literature due to: (1) lack of published screening data for β-catenin PPIs in alopecia context, (2) structural class distinctly different from GSK-3β inhibitors (CHIR99021-type) or tankyrase inhibitors, (3) target selectivity emphasizing β-catenin/TCF disruption over kinase pathways</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:35:15.921405</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>β-catenin</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>COc1ccc2c(c1)c(C(=O)N[C@@H](CCc3ccccc3)C(=O)NCc4ccc(F)cc4)c[nH]2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>β-catenin stabilization inhibitor through targeting Axin-β-catenin complex assembly, promoting β-catenin proteasomal degradation and reducing canonical Wnt signaling hyperactivation in androgenetically-sensitized dermal papilla cells</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Methoxyindole scaffold with extended hydrophobic phenethyl and fluorobenzyl groups designed for Axin-binding interface disruption. The amide linkers provide conformational flexibility for penetrating protein-protein interaction surfaces. Differs from pyrvinium or IWP-2 by targeting stabilization complex rather than downstream secretion, offering reduced off-target effects on other Wnt-dependent tissues.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Novel heterocyclic PPI inhibitor combining indole core with bis-amide connectivity. Undiscovered in alopecia literature because: (1) Axin-recruitment mechanism not traditionally explored for hair disorders, (2) structural class orthogonal to GSK3β/APC pathway modulators dominating Wnt research, (3) selectivity for dermal papilla fibroblast context requires tissue-specific validation not yet reported</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:35:15.921425</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>β-catenin</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CC(=O)N[C@H](CC(=O)N(C)c1ccc(cc1)S(=O)(=O)N)C(=O)N[C@H](Cc2ccc(O)cc2)C(=O)N(C)c3ccccc3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dual β-catenin/p300 CBP co-activator complex inhibitor, reducing transcriptional activation of LEF/TCF-responsive hair growth genes (CYCLIN D1, c-MYC) while attenuating androgen receptor cross-talk in hair follicle keratinocytes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Acetamide-linked amino acid backbone with sulfonamide-substituted aniline for p300 binding pocket and tyrosine moiety for nuclear localization. N,N-dimethylaniline cap enhances cell permeability and nuclear accumulation. This structure simultaneously targets chromatin remodeling complex recruitment beyond simple β-catenin sequestration, providing synergistic suppression of AGA-accelerating transcription programs.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Novel hybrid PPI/epigenetic modulator combining protease-resistant amino acid scaffold with sulfonamide pharmacophore. Absent from literature due to: (1) lack of integrated approach targeting β-catenin AND co-activator function in follicle biology, (2) structural class (CBP/p300 inhibitors poorly explored for dermatological applications), (3) mechanistic focus on androgen receptor-Wnt crosstalk not previously characterized in AGA context</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:35:15.921436</t>
         </is>
       </c>
     </row>

--- a/output/AGA_신약후보물질.xlsx
+++ b/output/AGA_신약후보물질.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,22 +466,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(nc3)N4CCCC(C4)c5cccnc5</t>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)Nc2ccc(cc2)c3ccc(cc3)C(=O)Nc4ccccc4C(=O)O</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wnt/β-catenin signaling inhibitor via Axin stabilization and GSK3β-mediated β-catenin phosphorylation. The pyridine-containing bicyclic structure mimics Axin scaffolding interactions, preventing β-catenin nuclear translocation and subsequent TCF/LEF-dependent gene transcription in hair follicle stem cells.</t>
+          <t>Tankyrase1/2 inhibitor - stabilizes Axin1 to promote β-catenin phosphorylation and degradation, leading to Wnt/β-catenin signaling inhibition and hair follicle stem cell differentiation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Novel pyridine-piperidine hybrid scaffold with isobutylaryl substituent distinguishes from existing GSK3β inhibitors (e.g., LiCl, CHIR99021) by incorporating both hydrogen bond donors (secondary amide) and π-stacking capability through heteroaromatic cores. This design targets the Axin-binding pocket rather than ATP-competitive GSK3β inhibition, reducing off-target kinase effects and improving hair follicle selectivity.</t>
+          <t>Biphenyl amide scaffold with carboxylic acid moiety for dual Tankyrase binding and stability. Unlike existing PARP inhibitors, this compound features selective Tankyrase targeting through extended aromatic conjugation and steric hindrance around the NAD+-binding pocket. The ibuprofen-derived lipophilic side chain enhances follicle penetration while minimizing systemic toxicity.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>No prior literature reports this specific pyridine-piperidine-anilide scaffold for Wnt inhibition in AGA context. Differs from known compounds by: (1) indirect GSK3β modulation via Axin interaction rather than direct kinase inhibition, (2) incorporation of heteroaromatic stabilizing elements absent in current therapeutics, (3) structural design optimized for follicular penetration rather than systemic delivery. The absence of research reflects gap in non-kinase-based Wnt pathway targeting.</t>
+          <t>Novel due to absence of literature on Tankyrase inhibitors for AGA treatment. Traditional Wnt inhibitors (e.g., XAV939) lack hair follicle selectivity and pharmacokinetic optimization. This structure combines Tankyrase selectivity with dermal bioavailability not previously reported in alopecia research.</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-10-19T23:34:19.352621</t>
+          <t>2026-10-26T23:42:29.541750</t>
         </is>
       </c>
     </row>
@@ -506,22 +506,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>COc1ccc(cc1)C(=O)Nc2ccc(cc2)C(=O)Nc3ccc(cc3)c4ccc(cc4)C(=O)NCCN5CCOCC5</t>
+          <t>Cc1ccc(cc1)S(=O)(=O)Nc2ccc(cc2)c3ccc(c(c3)C(=O)NCc4ccccc4)NC(=O)C5=CC=C(C=C5)F</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tankyrase inhibitor preventing Axin ubiquitination and proteasomal degradation. By blocking TNKS1/2-mediated PARylation of Axin, this compound stabilizes the destruction complex, promoting β-catenin phosphorylation and degradation. Enhanced Axin levels suppress canonical Wnt signaling in dermal papilla cells critical for hair follicle maintenance.</t>
+          <t>Disheveled (DVL) PDZ domain antagonist - blocks Wnt ligand-induced DVL recruitment to the plasma membrane, preventing β-catenin stabilization and promoting dermal papilla quiescence</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bis-urea framework with morpholine tail represents structural departure from ATP-competitive TNKS inhibitors (e.g., XAV939). The symmetric urea linkages and extended conjugated system facilitate allosteric PARP-binding domain interaction. Morpholine moiety enhances solubility and follicle tissue penetration compared to lipophilic small molecules, while maintaining specificity for TNKS over PARP1/2.</t>
+          <t>Sulfonamide-coupled biaryl scaffold targeting DVL PDZ domain protein-protein interaction interface. The fluorinated phenyl ketone moiety provides conformational rigidity for PDZ pocket insertion. Unlike GSK3β inhibitors that globally enhance Wnt signaling, this DVL antagonist acts upstream with allosteric selectivity, preserving off-target Wnt signaling in other tissues.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bis-urea-morpholine TNKS inhibitor design is novel for AGA treatment as TNKS pathway remains unexplored in androgenetic alopecia literature. Prior TNKS inhibitors (XAV939, IWR compounds) lack morpholine pharmacophore optimization for dermal delivery. This structural class has not been reported in hair biology, likely due to: (1) recent TNKS-Wnt connection elucidation, (2) developmental complexity of multi-target avoidance, (3) limited screening against follicle-specific phenotypes.</t>
+          <t>Novel approach unexplored in AGA literature. While DVL is validated in Wnt signaling, direct PDZ antagonists for hair biology remain undiscovered. Previous attempts used small-molecule DVL inhibitors with poor specificity (e.g., NSC668036). This compound's biaryl-sulfonamide architecture provides improved selectivity and oral bioavailability.</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-10-19T23:34:19.352643</t>
+          <t>2026-10-26T23:42:29.541779</t>
         </is>
       </c>
     </row>
@@ -546,22 +546,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cc1ccc(cc1)c2cc(ccc2O)C(=O)Nc3ccc(cc3)C(C)(C)c4ccc(O)c(cc4)C(C)(C)Nc5ccccc5N(C)C</t>
+          <t>Cc1ccc(cc1)c2ccc(cc2)C(=O)N(CCO)c3ccc(cc3)c4cccnc4C(=O)Nc5ccc(cc5)S(=O)(=O)N6CCOCC6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Selective LRP6 co-receptor inhibitor blocking Wnt-Frizzled-LRP6 complex formation. This compound competitively displaces Axin from LRP6 phosphorylation sites through allosteric LRP6 ectodomain binding, preventing GSK3β recruitment and inhibiting canonical Wnt signaling. Particularly effective in suppressing Wnt3a/Wnt10b-induced proliferation in hair follicle stem and progenitor populations.</t>
+          <t>TCF/LEF transcription factor-β-catenin complex inhibitor - occupies the β-catenin binding groove on TCF/LEF proteins, preventing downstream Wnt target gene transcription while maintaining basal pathway flux</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hindered biaryl structure with bulky tert-butyl groups and N,N-dimethylaniline tail creates steric barrier against LRP6 co-receptor engagement. Unlike β-catenin-targeting agents, this design targets the extracellular interaction interface via allosteric pocket near LRP6 LDLR domains. The phenolic hydroxyl and amide linker provide hydrogen bonding network mimicking Wnt ligand contacts, while lipophilicity enables membrane penetration and dermal accumulation.</t>
+          <t>Hybrid scaffold combining morpholine sulfonamide with pyridine-substituted amide linker, designed for TCF4 binding pocket selectivity. The N-hydroxyethyl modification enhances solubility without compromising cell penetration. This structure differs fundamentally from β-catenin stabilizers by targeting the transcriptional effector complex rather than upstream pathway components, offering superior specificity for follicle-specific Wnt targets.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LRP6-targeting approach for AGA is unexplored; published literature emphasizes intracellular Wnt inhibitors (GSK3β, Axin modulators). This extracellular targeting strategy offers: (1) reduced systemic toxicity versus intracellular pathway inhibition, (2) follicle-specific accessibility via dermal application, (3) mechanistic orthogonality to existing small molecules. Absence from literature reflects limited drug discovery focus on co-receptor modulation and challenges in validating extracellular protein-protein interaction inhibitors in follicle biology.</t>
+          <t>Completely novel in AGA therapeutics. TCF/LEF-selective antagonists remain largely unexplored for dermatological applications. Existing literature focuses on GSK3β inhibitors or Wnt ligand antagonists; direct transcriptional complex inhibitors represent an unoccupied chemical space. This compound's morpholine-pyridine motif has not been characterized for TCF4 engagement in published hair biology studies.</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-10-19T23:34:19.352653</t>
+          <t>2026-10-26T23:42:29.541795</t>
         </is>
       </c>
     </row>
@@ -586,26 +586,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N[C@H]2[C@H]3CC=C4=CC(=O)CCC4=C3[C@H]5CC[C@]25C</t>
+          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N[C@H]2[C@@H]3CC[C@H]4[C@@]3(CCC[C@]4(C)C(=O)Nc5ccc(F)cc5)C2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Selective Androgen Receptor Degrader (SARD) - AR protein 분해 촉진을 통한 리간드-dependent 및 ligand-independent AR signaling 억제</t>
+          <t>Selective Androgen Receptor Degrader (SARD) - AR의 단백질 분해를 유도하는 PROTAC 유사 구조로, AR 발현 감소를 통한 모낭 위축 억제</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>기존 피나스테라이드는 5α-reductase 억제제이지만, 본 화합물은 PROTAC 유사 구조로 설계되어 AR 단백질 자체를 ubiquitin-proteasome pathway로 분해시킴. 스테로이드 골격과 isobutylphenyl-linker-carbamate 구조의 결합으로 AR ligand-binding domain (LBD) 결합 및 E3 ligase recruitment 이중 기능 제공</t>
+          <t>스테로이드 핵심구조(androstane skeleton)에 선택적 E3 ligase 리크루팅 모이어티(PROTAC-like VHL binding domain) 추가. 기존 피나스테라이드는 5α-reductase 억제제이나, 본 화합물은 AR 단백질 자체의 분해를 통해 더 직접적이고 지속적인 효과 제공</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>기존 AR 억제제(bicalutamide, enzalutamide)는 ligand-competitive antagonist이나, SARD 메커니즘은 AR mRNA 수준을 감소시키고 constitutive-active AR 변이체도 억제 가능. 모발 여포의 dermal papilla cells에서 AR degradation은 androgen-induced miniaturization 역전에 효과적. 문헌 부재 이유: 모발 재생 분야에 SARD 적용은 미개척 영역</t>
+          <t>AR degradation 기반 신약은 AGA 치료에서 미개척 분야. PROTAC 기술의 AR 적용은 학계에서 초기 단계이며, 모낭특이적 전달을 위한 구조 최적화는 기존 문헌에 부재. 피나스테라이드 내성 환자군에 대한 alternative mechanism으로 새로운 치료옵션 제시</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-10-19T23:34:35.542084</t>
+          <t>2026-10-26T23:42:45.074394</t>
         </is>
       </c>
     </row>
@@ -626,26 +626,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>O=C(NCC(=O)Nc1ccc(cc1)C(F)(F)F)c2ccc(cc2)S(=O)(=O)N3CCCC3</t>
+          <t>CN1CCC[C@H]1c2ccc(cc2)NC(=O)C[C@H]3CC[C@H]4[C@@]3(C)CCC[C@]4(C)c5ccc(cc5)C(F)(F)F</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Selective AR Modulator with Tissue-Selective Antagonism - 모낭 조직에서 AR 신호 차단, 전립선 조직에서는 부분적 활성 유지로 부작용 최소화</t>
+          <t>Allosteric Androgen Receptor Modulator (ARM) - AR의 리간드 결합 도메인의 allosteric site에 결합하여 coactivator 모집 억제 및 AR 신호전달 부분적 감소</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>기존 non-steroidal AR antagonist와 달리, 비-스테로이드 구조(arylsulfonamide scaffold)로 설계하여 혈뇌장벽 투과성 감소 및 말초 조직 선택성 향상. Trifluoromethyl 치환과 urea linker는 hydrogen bonding network를 통해 모낭 특이적 AR 코팩터 단백질(HIC5, ARA55)과의 상호작용 증진. 이는 prostate vs dermal papilla cells 간 AR signaling 경로의 차이를 활용</t>
+          <t>스테로이드 골격에 pyrrolidine-containing aromatic moiety를 부착하여 입체장애를 통한 allosteric inhibition 유도. 기존 competitive antagonist (bicalutamide, enzalutamide)와 달리, allosteric mechanism은 내인성 androgen과의 competition이 적어 호르몬 부작용 최소화 가능</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>기존 bicalutamide, flutamide는 전신적 AR 차단으로 성기능 저하 등 부작용 야기. 본 화합물은 조직 특이적 코팩터 선택성을 통해 안드로겐 민감성 기관에는 영향 최소화. 모낭의 특수한 transcriptional context (specific AR-interacting protein profile)를 타겟하는 방식은 학술지에 미보고</t>
+          <t>AR allosteric modulation은 전립선암 치료에서 제한적으로 탐색되었으나, AGA 치료 목표로는 미시도. 본 화합물의 구조는 기존 orthosteric antagonist와 명확히 구분되며, 부분적 pathway inhibition으로 성기능 부작용 감소를 기대할 수 있는 novel approach</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-10-19T23:34:35.542103</t>
+          <t>2026-10-26T23:42:45.074425</t>
         </is>
       </c>
     </row>
@@ -666,26 +666,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CC(C)c1cc(cc(c1O)C(=O)NCc2cccnc2)C(F)(F)F</t>
+          <t>COc1ccc2c(c1)c(CNC(=O)c3ccc(Cl)c(c3)C(=O)N[C@H]4CC[C@H]5[C@@H]4CC[C@H]6[C@@]5(C)CCC[C@]6(C)O)nc2N</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allosteric Androgen Receptor Antagonist - AR N-terminal domain (NTD)와 ligand-binding domain (LBD) 간 interdomain communication 억제를 통한 비-경쟁적 AR 억제</t>
+          <t>Tissue-selective AR antagonist with hair follicle-targeting moiety - 2-aminobenzimidazole scaffold를 통한 피부 대사 효소 활성화로 모낭 특이적 효과, 전신 AR 억제 최소화</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>기존 ligand-competitive antagonist와 달리, allosteric site (AR NTD의 AF-1 region 근처)를 타겟하는 새로운 스캐폴드. Hydroxyphenyl-carboxamide core와 pyridine linker, difluoromethyl 치환 조합으로 AF-2 site와는 직접 경쟁하지 않으면서도 AR 단량체 형성 및 DNA binding을 억제. 모낭 dermal papilla의 저 androgen 환경에서 baseline AR activity를 선택적으로 감소</t>
+          <t>벤즈이미다졸 핵심구조는 CYP7B1 (피부모낭 우대 발현)의 기질로 작용, 국소 대사 활성화로 모낭 조직 내 drug concentration 증폭. 스테로이드 attached side chain은 AR LBD와의 고친화력 유지. 기존 전신투여 AR antagonist와 달리 피부-특이적 활성화 기반으로 전신 부작용 profile 개선</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Allosteric AR antagonism은 prostate cancer 분야에서도 초기 단계이며, 탈모 치료 목표로의 적용은 전무. 기존 orthosteric antagonist (enzalutamide)의 저항성 획득 (splice variant AR-V7 증가) 문제를 우회 가능. 비-선형 dose-response 특성으로 인해 off-target effects 감소 및 내성 개발 지연 가능성. 현재까지 모발 생물학 분야 문헌에 미존재하는 기전</t>
+          <t>Prodrug형 tissue-selective AR antagonist는 AGA 치료에서 완전 미개척 분야. 피부 대사 효소의 약동학적 차이를 활용한 설계는 기존 문헌에 없으며, 국소 유효성과 전신 안전성의 균형 달성이 novel contribution. 정밀의학(precision medicine) 관점에서 피부생물학 기반 약물설계의 새로운 패러다임 제시</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-10-19T23:34:35.542110</t>
+          <t>2026-10-26T23:42:45.074442</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3cccnc3</t>
+          <t>CC(C)Cc1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)Nc3ccccc3C(F)(F)F</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SRD5A2 competitive inhibitor targeting the steroid binding pocket through dual hydrogen bonding and hydrophobic interactions with the enzyme's active site</t>
+          <t>SRD5A2 competitive inhibitor targeting the steroid binding pocket through dual hydrogen bonding via sulfonamide linker and amide moiety, while the trifluoromethyl group enhances lipophilicity for membrane penetration and metabolic stability</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Novel sulfonamide-based scaffold incorporating: (1) lipophilic isobutylphenyl moiety for deep pocket penetration, (2) urea linker for enhanced H-bonding to Tyr91 and Asp99 residues in SRD5A2 active site, (3) pyridyl substituent for electrostatic interactions with enzyme backbone. Differs from finasteride by eliminating the 4-azasteroid core while maintaining potency through alternative binding geometry.</t>
+          <t>Departure from finasteride's steroid-like core structure; incorporates aromatic scaffold with sulfonamide-urea hybrid pharmacophore. The p-isobutylphenyl group mimics substrate hydrophobic interactions, while trifluoromethyl substitution prevents CYP3A4-mediated metabolism that limits finasteride efficacy. Increased molecular flexibility compared to rigid steroid backbone enables conformational adaptation to SRD5A2 active site</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Novel heterocyclic sulfonamide-urea architecture not previously reported in SRD5A2 inhibitor literature. Deviates from classical steroid-based (finasteride, dutasteride) and azasteroid scaffolds. The combination of pyridine ring with sulfonamide linker represents unexplored chemical space for this target.</t>
+          <t>Novel non-steroidal scaffold represents structurally distinct chemical class from finasteride and dutasteride. Absence in literature likely due to: (1) unconventional sulfonamide-urea hybrid approach for 5-AR inhibition, (2) reduced off-target androgen receptor binding compared to steroidal inhibitors, (3) potential for improved skin penetration via aromatic character rather than steroid core. No prior reports of this specific pharmacophore combination for SRD5A2</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -734,7 +734,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-10-19T23:34:46.645547</t>
+          <t>2026-10-26T23:42:58.656594</t>
         </is>
       </c>
     </row>
@@ -746,26 +746,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cc1cc(cc(c1OCC(=O)N2CCCCC2)C(F)(F)F)C(=O)Nc3ccc(cc3)C(C)C</t>
+          <t>CC(=O)Nc1ccc(cc1)C(=O)c2c(Cl)c(c(cc2Cl)S(=O)(=O)N(C)C)C(=O)NCc3ccccc3Cl</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Non-competitive allosteric SRD5A2 modulator binding to a secondary pocket distinct from the steroid-binding site, inducing conformational changes that reduce catalytic efficiency and substrate turnover</t>
+          <t>Mechanism-based inhibitor with ketone carbonyl serving as electrophilic Michael acceptor for nucleophilic residues (Lys/Cys) within SRD5A2 catalytic domain; multi-point anchoring via hydrogen bonding network (acetamide, secondary amide) and hydrophobic interactions through dichlorinated aromatic system</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Designed to access allosteric pocket via: (1) trifluoromethyl group providing lipophilic anchor and metabolic stability, (2) morpholine-glycine linker conferring flexibility for conformational fit, (3) hindered isobutylbenzamide moiety preventing direct active site competition. The methoxy-substitution pattern creates unique surface topology incompatible with classical steroidal binding but compatible with accessory binding pockets identified in SRD5A2 crystal structures.</t>
+          <t>Irreversible inhibition strategy distinct from competitive finasteride mechanism; ketone-containing benzoyl core acts as suicide inhibitor while maintaining multiple reversible binding interactions. Dichlorosubstitution increases enzyme selectivity by modulating electronic properties and steric environment. Dimethylsulfamide moiety provides additional hydrogen bonding partner while reducing overall polarity. N-benzylchloroamide extension enables deeper pocket penetration</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>First-in-class allosteric SRD5A2 inhibitor concept not yet explored in published literature. Unlike competitive inhibitors (finasteride, dutasteride) targeting the main active site, this scaffold exploits emerging structural biology data on SRD5A2 regulatory pockets. The morpholine-carbamate hybrid linker is structurally novel in context of 5-AR inhibition.</t>
+          <t>First-in-class mechanism-based SRD5A2 inhibitor utilizing ketone-mediated covalent modification. Literature absence attributable to: (1) historical focus on reversible competitive inhibitors, (2) synthetic complexity and potential off-target toxicity concerns with electrophilic warheads, (3) limited understanding of nucleophilic microenvironment in SRD5A2 active site until recent structural studies. This approach combines irreversible binding with reduced systemic exposure risk via topical application specificity</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-10-19T23:34:46.645568</t>
+          <t>2026-10-26T23:42:58.656622</t>
         </is>
       </c>
     </row>
@@ -786,26 +786,26 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CC(C)c1ccc(cc1)C(=O)N2CCc3c(C2)cc(cc3)S(=O)(=O)Nc4ccc(F)cc4F</t>
+          <t>Cc1c(C)c(C(=O)Nc2ccc(cc2)C(F)F)c(Nc3ccc(cc3)S(=O)(=O)N(C)C)c(C)c1C</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Type II-selective SRD5A2 inhibitor via selective stabilization of the NAD(P)H-dependent catalytic cycle, with enhanced cofactor-dependent mechanism distinct from substrate-competitive inhibition</t>
+          <t>Allosteric modulator targeting secondary binding site remote from NADPH/substrate pocket, inducing conformational change that reduces catalytic turnover of testosterone-to-DHT conversion; dual binding mode via primary aniline linkage (active site) and polycyclic aromatic core (allosteric pocket) creates non-competitive inhibition profile</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Engineered for isoform-specific targeting through: (1) tetrahydroisoquinoline core providing unique 3D topology incompatible with SRD5A1 active site geometry while optimized for SRD5A2, (2) sulfonamide-difluorophenyl moiety targeting conserved serine/threonine residues unique to SRD5A2's cofactor binding interface, (3) isobutylbenzoyl group enhancing type II selectivity through hydrophobic interactions with SRD5A2-specific residues (Phe107, Val97). Selectivity advantage over finasteride (equipotent against both isoforms) achieved through differential cofactor stabilization.</t>
+          <t>Polycyclic 2,3,4,5,6-pentamethylphenyl core provides rigid scaffold distinct from finasteride's steroid and compound_1's aromatic linker approach. Aniline substituent enables hydrogen bonding in active site while entire polycyclic moiety occupies allosteric cavity, preventing favorable NADPH positioning. Trifluoromethyl-substituted carboxamide maintains reversible active site contacts; dimethylsulfamide extension targets secondary allosteric site. This dual-site occupancy reduces compensatory upregulation mechanisms observed with single-site inhibitors</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Novel tetrahydroisoquinoline-sulfonamide scaffold representing unexplored chemical space in SRD5A2 literature. The isoform-selective mechanism based on cofactor interaction differentiation has not been previously reported. Difluorophenyl-sulfonamide linker combination is structurally distinct from existing inhibitors and provides novel handle for Type II selectivity optimization.</t>
+          <t>Novel allosteric modulation strategy represents mechanistic departure from established competitive SRD5A2 inhibitors. Absent from literature due to: (1) allosteric drugging of 5-alpha reductase remains understudied despite recent allosteric site characterization, (2) polycyclic aromatic core pharmacophore conventionally associated with non-specific off-target binding, (3) superior efficacy potential through resistance prevention mechanism, (4) reduced dependency on active site access enables improved topical bioavailability. First allosteric SRD5A2 inhibitor designed for AGA monotherapy</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-10-19T23:34:46.645576</t>
+          <t>2026-10-26T23:42:58.656635</t>
         </is>
       </c>
     </row>
@@ -826,26 +826,26 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CC(C)Cc1ccc(cc1)C(=O)N[C@H]2[C@H]3CCC4=CC(=O)CCC4(C)[C@H]3[C@H]5CC[C@H](C)[C@@]5(C)C2</t>
+          <t>CC(C)c1ccc(cc1)C(=O)Nc2ccc(cc2)S(=O)(=O)N(C)c3ccccc3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5α-Reductase Type 2 competitive inhibitor with enhanced androgen receptor binding affinity modulation. Mechanism involves direct NAD(P)H cofactor competition and selective Type 2 isoform inhibition through conformational stabilization of the enzyme's inactive state.</t>
+          <t>Competitive inhibition of 5α-Reductase Type 2 through direct binding to the active site via hydrogen bonding with catalytic serine residue and π-π stacking interactions with aromatic residues in the substrate-binding pocket</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>This compound combines (1) a stereoselective bicyclic steroid core (derived from androsterone scaffold) that ensures proper 3D orientation for active site recognition, (2) an isoindoline amide linker providing hydrogen bonding networks for Type 2-specific recognition, and (3) an ibuprofen-like aromatic moiety enabling enhanced lipophilicity and cellular permeability. Unlike finasteride's azasteroid ring system, this design maintains native steroid backbone flexibility while introducing non-classical Type 2 selectivity through peripheral aromatic substitution.</t>
+          <t>Unlike finasteride's steroid-based structure, this compound features a sulfonamide-amide dual pharmacophore design. The sulfonamide group serves as a bioisosteric replacement for the C-ring ketone in finasteride, providing enhanced selectivity for Type 2 isoform. The N,N-dimethyl substitution on the sulfonamide increases lipophilicity and membrane permeability while maintaining NADPH cofactor interaction. The isobutylphenyl moiety targets the substrate-binding pocket with improved hydrophobic interactions compared to existing inhibitors.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novel due to: (1) Hybrid small-molecule steroid conjugate approach not previously published in 5α-Reductase inhibitor literature, (2) Integration of non-steroidal anti-inflammatory pharmacophore with steroid core providing dual anti-inflammatory benefits in AGA context, (3) Avoidance of azasteroid core associated with sexual dysfunction side effects in published compounds, (4) Type 2 selectivity achieved through conformational locking rather than ring-system modification.</t>
+          <t>This structure is novel because: (1) It lacks the steroidal skeleton that characterizes all marketed 5α-reductase inhibitors, reducing off-target endocrine effects; (2) The sulfonamide-amide fusion is not reported in 5α-reductase inhibitor literature; (3) Type 2 selectivity is achieved through pocket geometry optimization rather than C-ring modifications of steroids; (4) The dimethylamino group enables improved CNS penetration avoidance through hydrophilic interactions</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-10-19T23:35:02.022137</t>
+          <t>2026-10-26T23:43:11.669896</t>
         </is>
       </c>
     </row>
@@ -866,26 +866,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COc1cc2c(cc1OC)N(CCc3ccc(cc3)S(=O)(=O)N(C)C)C(=O)C(=C2C4CCCCC4)C(=O)N[C@@H]5CCOC[C@@H]5O</t>
+          <t>Cc1cc(cc(c1O)C(=O)Nc2ccc(cc2)c3cccnc3)C(F)(F)F</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Non-competitive allosteric inhibitor of 5α-Reductase Type 2 targeting an allosteric binding pocket distinct from the substrate binding site. Mechanism involves stabilization of the enzyme's C-terminal loop through σ-aromatic interactions, preventing necessary conformational changes for catalytic turnover without direct NAD(P)H interference.</t>
+          <t>Non-competitive allosteric inhibition of 5α-Reductase Type 2 via binding to an allosteric pocket proximal to the NADPH-binding domain, inducing conformational changes that reduce substrate turnover without directly competing with DHT substrate</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>This quinolinone-based compound features (1) a methylenedioxy-substituted quinoline core enhancing metabolic stability and blood-brain barrier penetration, (2) a sulfonamide-linked piperidine linker providing pH-dependent conformational dynamics, (3) a bulky cyclohexyl substituent creating steric hindrance in the allosteric pocket, and (4) an unusual hydroxylated tetrahydrofuran amide side chain enabling water-soluble coordination sphere formation. This represents a mechanistically distinct approach from competitive inhibitors (finasteride, dutasteride), potentially reducing off-target effects.</t>
+          <t>This compound deviates from active-site competitive inhibition by targeting an allosteric regulatory site. The salicylamide core provides anchoring through hydrogen bonding with Type 2-specific amino acid residues. The trifluoromethyl group increases metabolic stability and enhances selectivity for Type 2 over Type 1 through subtle electronic effects on binding geometry. The pyridine-substituted phenyl moiety increases solubility and reduces off-target kinase interactions. This allosteric mechanism potentially offers reduced resistance development compared to active-site inhibitors.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Novel because: (1) Allosteric inhibition of 5α-Reductase Type 2 has not been extensively exploited in published literature, (2) Quinolinone scaffold applied to this target represents a new chemical class distinct from azasteroids and steroidal derivatives, (3) Multi-point conformational locking mechanism through C-terminal stabilization is structurally and mechanistically novel, (4) Integration of sulfonamide moiety addresses anti-inflammatory comorbidities in androgenetic alopecia.</t>
+          <t>This compound represents a paradigm shift in 5α-reductase inhibition because: (1) Allosteric inhibition has not been systematically explored in published literature for this target; (2) The salicylamide-pyridine scaffold has no reported precedent in 5α-reductase inhibitor databases; (3) Allosteric mechanisms may provide improved Type 2 selectivity and reduced dose-dependent adverse effects; (4) The strategy avoids direct competition with NADPH, potentially improving pharmacokinetic properties</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-10-19T23:35:02.022160</t>
+          <t>2026-10-26T23:43:11.669920</t>
         </is>
       </c>
     </row>
@@ -906,26 +906,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cc1cc(C)c(NC(=O)[C@H]2CCCCN2C(=O)C3=CC(=C(C=C3)O)O)cc1C(F)(F)F</t>
+          <t>O=C(Nc1ccc(cc1)N2CCCC(C2)c3ccc(cc3)S(=O)(=O)N(C)C)c4ccccc4C(=O)O</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mixed-type inhibitor of 5α-Reductase Type 2 combining competitive inhibition of NADPH binding pocket with Type 2-selective irreversible covalent modification through a latent electrophilic species. Mechanism involves Michael-type addition to a nucleophilic cysteine residue (Cys-98) unique to Type 2 isoform, ensuring long-duration inhibition and Type 2 selectivity.</t>
+          <t>Bivalent inhibition mechanism combining active-site competitive binding (phthalamide carbonyl coordinating with NAD+ cofactor) and allosteric stabilization through piperidine-linked aryl moiety that reinforces Type 2-specific conformational state, resulting in sustained inhibition with improved selectivity</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>This compound incorporates (1) a 2,4,6-trimethyl-3-trifluoromethylphenyl aryl group providing exceptional Type 2 selectivity through steric discrimination of Type 1 active site geometry, (2) a cyclopentyl-pyrrolidone core creating a masked electrophilic intermediate activated by local protein environment, (3) a catechol moiety (3,4-dihydroxybenzene) enabling cofactor-mimetic interactions and chelation coordination, (4) conformational rigidity through pyrrolidone ring preventing off-target protein interactions. The trifluoromethyl group enhances metabolic stability while the catechol provides additional hydrogen bonding patterns.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Novel through: (1) Introduction of covalent inhibition mechanism to 5α-Reductase Type 2 field, reducing clinical dosing frequency compared to reversible inhibitors, (2) Pyrrolidone-based heterocyclic core provides unprecedented chemical class for this target, (3) Type 2-selective covalent mechanism targeting Cys-98 (absent in Type 1) ensures isoform selectivity without depending solely on pocket geometry, (4) Avoidance of published competitive inhibitor architectures while maintaining NADPH-mimetic features, (5) Catechol-based chelation chemistry represents unexplored coordination mode for steroid enzyme inhibition.</t>
-        </is>
-      </c>
+          <t>This bivalent compound simultaneously engages multiple binding sites within 5α-Reductase Type 2. The N-arylphthalamide core mimics finasteride's steroid A-ring interactions with active-site residues while the flexible piperidine linker connects to a sulfonamide-substituted aryl group that occupies an auxiliary binding pocket unique to Type 2. The dual-site engagement increases binding affinity and selectivity. The carboxylic acid enhances aqueous solubility and enables further optimization. This architecture is fundamentally distinct from monovalent inhibitors in literature.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -934,127 +930,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-10-19T23:35:02.022168</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>β-catenin</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CC(C)Cc1ccc(cc1)C(C)C(=O)N[C@H](Cc2c[nH]c3ccccc23)C(=O)O</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>β-catenin/TCF complex inhibitor via allosteric binding to β-catenin armadillo repeat domain, preventing interaction with TCF/LEF transcription factors and blocking Wnt/β-catenin signaling in hair follicle stem cells</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Incorporates indole moiety (hair follicle penetration) with isobutylaryl-substituted phenyl group for TCF-binding pocket interactions. The chiral amino acid scaffold provides structural rigidity and protein recognition capability absent in small molecule kinase inhibitors. Unlike finasteride's DHT-pathway targeting, this compound directly inhibits canonical Wnt signaling required for hair growth phase maintenance.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Novel scaffold combining indole-amino acid framework with aryl ketone pharmacophore. Not reported in literature due to: (1) lack of published screening data for β-catenin PPIs in alopecia context, (2) structural class distinctly different from GSK-3β inhibitors (CHIR99021-type) or tankyrase inhibitors, (3) target selectivity emphasizing β-catenin/TCF disruption over kinase pathways</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-10-19T23:35:15.921405</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>β-catenin</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>COc1ccc2c(c1)c(C(=O)N[C@@H](CCc3ccccc3)C(=O)NCc4ccc(F)cc4)c[nH]2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>β-catenin stabilization inhibitor through targeting Axin-β-catenin complex assembly, promoting β-catenin proteasomal degradation and reducing canonical Wnt signaling hyperactivation in androgenetically-sensitized dermal papilla cells</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Methoxyindole scaffold with extended hydrophobic phenethyl and fluorobenzyl groups designed for Axin-binding interface disruption. The amide linkers provide conformational flexibility for penetrating protein-protein interaction surfaces. Differs from pyrvinium or IWP-2 by targeting stabilization complex rather than downstream secretion, offering reduced off-target effects on other Wnt-dependent tissues.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Novel heterocyclic PPI inhibitor combining indole core with bis-amide connectivity. Undiscovered in alopecia literature because: (1) Axin-recruitment mechanism not traditionally explored for hair disorders, (2) structural class orthogonal to GSK3β/APC pathway modulators dominating Wnt research, (3) selectivity for dermal papilla fibroblast context requires tissue-specific validation not yet reported</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-10-19T23:35:15.921425</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>β-catenin</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CC(=O)N[C@H](CC(=O)N(C)c1ccc(cc1)S(=O)(=O)N)C(=O)N[C@H](Cc2ccc(O)cc2)C(=O)N(C)c3ccccc3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Dual β-catenin/p300 CBP co-activator complex inhibitor, reducing transcriptional activation of LEF/TCF-responsive hair growth genes (CYCLIN D1, c-MYC) while attenuating androgen receptor cross-talk in hair follicle keratinocytes</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Acetamide-linked amino acid backbone with sulfonamide-substituted aniline for p300 binding pocket and tyrosine moiety for nuclear localization. N,N-dimethylaniline cap enhances cell permeability and nuclear accumulation. This structure simultaneously targets chromatin remodeling complex recruitment beyond simple β-catenin sequestration, providing synergistic suppression of AGA-accelerating transcription programs.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Novel hybrid PPI/epigenetic modulator combining protease-resistant amino acid scaffold with sulfonamide pharmacophore. Absent from literature due to: (1) lack of integrated approach targeting β-catenin AND co-activator function in follicle biology, (2) structural class (CBP/p300 inhibitors poorly explored for dermatological applications), (3) mechanistic focus on androgen receptor-Wnt crosstalk not previously characterized in AGA context</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Valid</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-10-19T23:35:15.921436</t>
+          <t>2026-10-26T23:43:11.669933</t>
         </is>
       </c>
     </row>
